--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -1450,13 +1450,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46064.809313460646</v>
+        <v>46064.97598012732</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.573083449075</v>
+        <v>46092.73975011574</v>
       </c>
       <c r="D4" s="5">
-        <v>46127.420010173606</v>
+        <v>46127.58667684028</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1499,13 +1499,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46064.80931388889</v>
+        <v>46064.97598055555</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.57305327547</v>
+        <v>46092.739719942125</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.57308410879</v>
+        <v>46092.739750775465</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1564,13 +1564,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46064.809314212966</v>
+        <v>46064.97598087963</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.57305391204</v>
+        <v>46092.7397205787</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.57308402778</v>
+        <v>46092.73975069444</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1629,13 +1629,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46064.80931452547</v>
+        <v>46064.975981192125</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.57305435185</v>
+        <v>46092.739721018515</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.5730846875</v>
+        <v>46092.739751354165</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1694,13 +1694,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46064.80931484954</v>
+        <v>46064.9759815162</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.57305482639</v>
+        <v>46092.73972149305</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.62625699074</v>
+        <v>46100.79292365741</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1759,13 +1759,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46064.80931515046</v>
+        <v>46064.97598181713</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.57305549768</v>
+        <v>46092.73972216435</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.573090370366</v>
+        <v>46092.73975703704</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1824,11 +1824,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46064.80931546296</v>
+        <v>46064.97598212963</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46154.43040240741</v>
+        <v>46154.59706907407</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1871,13 +1871,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46064.80931575231</v>
+        <v>46064.97598241898</v>
       </c>
       <c r="C11" s="8">
-        <v>46112.484149675925</v>
+        <v>46112.65081634259</v>
       </c>
       <c r="D11" s="8">
-        <v>46112.48417648148</v>
+        <v>46112.65084314815</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1936,11 +1936,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46064.80931606481</v>
+        <v>46064.975982731485</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46160.51681480324</v>
+        <v>46160.68348146991</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -1999,13 +1999,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46064.80931635416</v>
+        <v>46064.975983020835</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.347010219906</v>
+        <v>46114.51367688658</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.34702380787</v>
+        <v>46114.51369047454</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2052,13 +2052,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46064.809306967596</v>
+        <v>46064.97597363426</v>
       </c>
       <c r="C14" s="5">
-        <v>46111.623314745375</v>
+        <v>46111.78998141203</v>
       </c>
       <c r="D14" s="5">
-        <v>46111.62331697917</v>
+        <v>46111.78998364584</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2117,13 +2117,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46064.80930760417</v>
+        <v>46064.975974270834</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.62332436343</v>
+        <v>46111.78999103009</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.6233259375</v>
+        <v>46111.78999260417</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2182,13 +2182,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46064.80930789352</v>
+        <v>46064.975974560184</v>
       </c>
       <c r="C16" s="5">
-        <v>46111.62333570602</v>
+        <v>46111.79000237268</v>
       </c>
       <c r="D16" s="5">
-        <v>46111.623337349534</v>
+        <v>46111.790004016206</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2247,13 +2247,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46064.80930815972</v>
+        <v>46064.97597482639</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34699280093</v>
+        <v>46114.51365946759</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.3470103125</v>
+        <v>46114.51367697917</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2312,13 +2312,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46064.8093084375</v>
+        <v>46064.97597510417</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.48433127315</v>
+        <v>46112.65099793981</v>
       </c>
       <c r="D18" s="5">
-        <v>46139.61509335648</v>
+        <v>46139.78176002315</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2361,13 +2361,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46064.80930898148</v>
+        <v>46064.97597564815</v>
       </c>
       <c r="C19" s="8">
-        <v>46111.623400972225</v>
+        <v>46111.79006763889</v>
       </c>
       <c r="D19" s="8">
-        <v>46111.62341542824</v>
+        <v>46111.79008209491</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2426,13 +2426,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46064.809308703705</v>
+        <v>46064.97597537037</v>
       </c>
       <c r="C20" s="5">
-        <v>46111.62341221065</v>
+        <v>46111.79007887731</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.623428101855</v>
+        <v>46111.79009476852</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -2491,13 +2491,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46064.80930923611</v>
+        <v>46064.97597590278</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.48430203703</v>
+        <v>46112.6509687037</v>
       </c>
       <c r="D21" s="8">
-        <v>46112.48433341435</v>
+        <v>46112.65100008102</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2556,13 +2556,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46064.809309502314</v>
+        <v>46064.97597616898</v>
       </c>
       <c r="C22" s="5">
-        <v>46111.62344167824</v>
+        <v>46111.79010834491</v>
       </c>
       <c r="D22" s="5">
-        <v>46111.62345855324</v>
+        <v>46111.79012521991</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2621,13 +2621,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46064.80930645834</v>
+        <v>46064.975973125</v>
       </c>
       <c r="C23" s="8">
-        <v>46111.62349084491</v>
+        <v>46111.790157511576</v>
       </c>
       <c r="D23" s="8">
-        <v>46111.62350752315</v>
+        <v>46111.79017418981</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2686,13 +2686,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46064.80930671297</v>
+        <v>46064.97597337963</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.597614976854</v>
+        <v>46114.76428164352</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.662779502316</v>
+        <v>46155.82944616898</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2735,13 +2735,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46064.809306967596</v>
+        <v>46064.97597363426</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.62412446759</v>
+        <v>46111.79079113426</v>
       </c>
       <c r="D25" s="8">
-        <v>46139.61514642361</v>
+        <v>46139.781813090274</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2800,13 +2800,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46064.820425868056</v>
+        <v>46064.98709253472</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.624070405094</v>
+        <v>46111.79073707176</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.62407200232</v>
+        <v>46111.79073866898</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2855,13 +2855,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46064.82027923611</v>
+        <v>46064.98694590278</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.624109212964</v>
+        <v>46111.79077587963</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.62411060186</v>
+        <v>46111.790777268514</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2910,13 +2910,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46064.809307812495</v>
+        <v>46064.975974479166</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.66277267361</v>
+        <v>46155.829439340276</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.66284179398</v>
+        <v>46155.82950846065</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2975,13 +2975,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46064.80930810185</v>
+        <v>46064.97597476852</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.48434800926</v>
+        <v>46112.651014675925</v>
       </c>
       <c r="D29" s="8">
-        <v>46112.48434962963</v>
+        <v>46112.651016296295</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3036,13 +3036,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46064.80930835648</v>
+        <v>46064.975975023146</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.39134616898</v>
+        <v>46154.55801283565</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.39134756944</v>
+        <v>46154.558014236114</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3097,13 +3097,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46064.80930862269</v>
+        <v>46064.97597528935</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.62398993055</v>
+        <v>46111.79065659722</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.62400064815</v>
+        <v>46111.79066731481</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3162,13 +3162,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46064.809306180556</v>
+        <v>46064.97597284723</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.62392708333</v>
+        <v>46111.79059375</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.62392899305</v>
+        <v>46111.790595659724</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3223,13 +3223,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46064.809306574076</v>
+        <v>46064.97597324074</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.62397100695</v>
+        <v>46111.79063767361</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.6239724537</v>
+        <v>46111.79063912037</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3284,13 +3284,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46064.80930684028</v>
+        <v>46064.975973506946</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.62387822916</v>
+        <v>46111.79054489583</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.623891979165</v>
+        <v>46111.79055864584</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3349,13 +3349,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46064.80930710648</v>
+        <v>46064.97597377315</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.6238140162</v>
+        <v>46111.790480682874</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.62381521991</v>
+        <v>46111.79048188658</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3410,13 +3410,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46064.80930738426</v>
+        <v>46064.975974050925</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.623850648146</v>
+        <v>46111.79051731482</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.62385216435</v>
+        <v>46111.79051883102</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3471,13 +3471,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46064.80930765046</v>
+        <v>46064.97597431713</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.62386230324</v>
+        <v>46111.79052896991</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.62386381945</v>
+        <v>46111.79053048611</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3532,13 +3532,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46064.80930792824</v>
+        <v>46064.97597459491</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.62376377315</v>
+        <v>46111.79043043981</v>
       </c>
       <c r="D38" s="5">
-        <v>46139.61517496528</v>
+        <v>46139.78184163195</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3597,13 +3597,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46064.80930820602</v>
+        <v>46064.97597487269</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.62370167824</v>
+        <v>46111.79036834491</v>
       </c>
       <c r="D39" s="8">
-        <v>46111.62370304398</v>
+        <v>46111.79036971065</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3658,13 +3658,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46064.8093084838</v>
+        <v>46064.97597515046</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.6237495949</v>
+        <v>46111.790416261574</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.62375113426</v>
+        <v>46111.79041780093</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3719,13 +3719,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46064.809307881944</v>
+        <v>46064.97597454861</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.60195364583</v>
+        <v>46114.768620312505</v>
       </c>
       <c r="D41" s="8">
-        <v>46139.61497306713</v>
+        <v>46139.781639733796</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3768,13 +3768,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.50289251158</v>
+        <v>46070.66955917824</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.34715076389</v>
+        <v>46114.513817430554</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.34716959491</v>
+        <v>46114.51383626157</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3833,13 +3833,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46064.8093081713</v>
+        <v>46064.97597483796</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.347206666665</v>
+        <v>46114.51387333333</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.3472219213</v>
+        <v>46114.513888587964</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3898,13 +3898,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46087.336886377314</v>
+        <v>46087.50355304398</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.34725474537</v>
+        <v>46114.513921412035</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.347268784724</v>
+        <v>46114.51393545139</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3963,13 +3963,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46087.3369296412</v>
+        <v>46087.50359630787</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.6019366088</v>
+        <v>46114.768603275465</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.014816875</v>
+        <v>46127.181483541666</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4026,13 +4026,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46064.80930847222</v>
+        <v>46064.97597513889</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.54886012731</v>
+        <v>46107.71552679398</v>
       </c>
       <c r="D46" s="5">
-        <v>46139.61487302084</v>
+        <v>46139.7815396875</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4075,13 +4075,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46064.80930877315</v>
+        <v>46064.97597543981</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.54884430555</v>
+        <v>46107.71551097222</v>
       </c>
       <c r="D47" s="8">
-        <v>46139.61481119213</v>
+        <v>46139.78147785879</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4140,13 +4140,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46064.809309062504</v>
+        <v>46064.97597572916</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.548765451385</v>
+        <v>46107.71543211806</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.61483048611</v>
+        <v>46139.78149715278</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4205,13 +4205,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46064.80930936342</v>
+        <v>46064.975976030095</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.54899877315</v>
+        <v>46107.71566543981</v>
       </c>
       <c r="D49" s="8">
-        <v>46139.61478167824</v>
+        <v>46139.781448344904</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4254,13 +4254,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46064.809309652774</v>
+        <v>46064.975976319445</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.5485365625</v>
+        <v>46107.71520322916</v>
       </c>
       <c r="D50" s="5">
-        <v>46139.61468195602</v>
+        <v>46139.78134862268</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4319,13 +4319,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46064.80931</v>
+        <v>46064.97597666667</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.54864957176</v>
+        <v>46107.71531623843</v>
       </c>
       <c r="D51" s="8">
-        <v>46139.61470181713</v>
+        <v>46139.7813684838</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4384,13 +4384,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46064.80930681713</v>
+        <v>46064.9759734838</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.548982719905</v>
+        <v>46107.71564938658</v>
       </c>
       <c r="D52" s="5">
-        <v>46139.61473543981</v>
+        <v>46139.781402106484</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4447,13 +4447,13 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46064.80930719907</v>
+        <v>46064.975973865745</v>
       </c>
       <c r="C53" s="8">
-        <v>46155.66268663194</v>
+        <v>46155.82935329861</v>
       </c>
       <c r="D53" s="8">
-        <v>46155.66268811343</v>
+        <v>46155.82935478009</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4496,13 +4496,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46064.80930784722</v>
+        <v>46064.97597451389</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.54818842592</v>
+        <v>46107.71485509259</v>
       </c>
       <c r="D54" s="5">
-        <v>46139.61443797454</v>
+        <v>46139.7811046412</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4559,13 +4559,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46064.809308449076</v>
+        <v>46064.97597511574</v>
       </c>
       <c r="C55" s="8">
-        <v>46154.39139984954</v>
+        <v>46154.558066516205</v>
       </c>
       <c r="D55" s="8">
-        <v>46155.66287702546</v>
+        <v>46155.82954369213</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>56</v>
@@ -4622,13 +4622,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46064.809307557865</v>
+        <v>46064.97597422454</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.548039201385</v>
+        <v>46107.71470586806</v>
       </c>
       <c r="D56" s="5">
-        <v>46139.614411400464</v>
+        <v>46139.78107806713</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4685,13 +4685,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.338309212966</v>
+        <v>46065.50497587963</v>
       </c>
       <c r="C57" s="8">
-        <v>46107.547905416664</v>
+        <v>46107.714572083336</v>
       </c>
       <c r="D57" s="8">
-        <v>46139.614389594906</v>
+        <v>46139.78105626158</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4748,13 +4748,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46064.809308993055</v>
+        <v>46064.97597565972</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.548378391206</v>
+        <v>46107.71504505787</v>
       </c>
       <c r="D58" s="5">
-        <v>46139.61459003472</v>
+        <v>46139.78125670139</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4797,13 +4797,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46064.80930925926</v>
+        <v>46064.975975925925</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.54835604166</v>
+        <v>46107.71502270833</v>
       </c>
       <c r="D59" s="8">
-        <v>46120.00679005787</v>
+        <v>46120.17345672454</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4862,13 +4862,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46064.80930957176</v>
+        <v>46064.97597623843</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.54703266204</v>
+        <v>46107.7136993287</v>
       </c>
       <c r="D60" s="5">
-        <v>46139.61447259259</v>
+        <v>46139.781139259256</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -4925,13 +4925,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46064.80930677083</v>
+        <v>46064.9759734375</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.54724788194</v>
+        <v>46107.713914548614</v>
       </c>
       <c r="D61" s="8">
-        <v>46139.61449416667</v>
+        <v>46139.78116083333</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>222</v>
@@ -4988,13 +4988,13 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46064.80930710648</v>
+        <v>46064.97597377315</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.547382916666</v>
+        <v>46107.71404958333</v>
       </c>
       <c r="D62" s="5">
-        <v>46139.614516898146</v>
+        <v>46139.78118356482</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5051,13 +5051,13 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46064.809307627314</v>
+        <v>46064.97597429398</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.547501354165</v>
+        <v>46107.71416802083</v>
       </c>
       <c r="D63" s="8">
-        <v>46126.04068769676</v>
+        <v>46126.207354363425</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5114,13 +5114,13 @@
         <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46064.809307881944</v>
+        <v>46064.97597454861</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.54765474537</v>
+        <v>46107.71432141204</v>
       </c>
       <c r="D64" s="5">
-        <v>46139.614540243056</v>
+        <v>46139.78120690973</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5177,11 +5177,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46064.809308125</v>
+        <v>46064.97597479167</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46126.62549803241</v>
+        <v>46126.79216469907</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5224,11 +5224,11 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46064.80930837963</v>
+        <v>46064.9759750463</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.66293737269</v>
+        <v>46155.82960403935</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5285,11 +5285,11 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46064.80930862269</v>
+        <v>46064.97597528935</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46154.43040266204</v>
+        <v>46154.59706932871</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5346,11 +5346,11 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46064.80930886574</v>
+        <v>46064.975975532405</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46139.00144871528</v>
+        <v>46139.168115381945</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5407,11 +5407,11 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46064.80930912037</v>
+        <v>46064.975975787034</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46140.001288680556</v>
+        <v>46140.16795534722</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>251</v>
@@ -5468,11 +5468,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46064.80930690972</v>
+        <v>46064.97597357639</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.62547358796</v>
+        <v>46126.792140254634</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>254</v>
@@ -5515,11 +5515,11 @@
         <v>256</v>
       </c>
       <c r="B71" s="8">
-        <v>46064.80930769676</v>
+        <v>46064.97597436343</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46150.00190105324</v>
+        <v>46150.168567719906</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>257</v>
@@ -5578,11 +5578,11 @@
         <v>260</v>
       </c>
       <c r="B72" s="5">
-        <v>46064.80930738426</v>
+        <v>46064.975974050925</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46150.0018987963</v>
+        <v>46150.16856546296</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>261</v>
@@ -5641,11 +5641,11 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.3650941088</v>
+        <v>46090.53176077546</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46126.62547373843</v>
+        <v>46126.792140405094</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5688,11 +5688,11 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.366989016205</v>
+        <v>46090.53365568287</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46149.00141920139</v>
+        <v>46149.168085868056</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5751,11 +5751,11 @@
         <v>269</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.3671906713</v>
+        <v>46090.53385733796</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46161.001197997684</v>
+        <v>46161.167864664356</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>270</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46154.59706907407</v>
+        <v>46196.784762916664</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1938,9 +1938,11 @@
       <c r="B12" s="5">
         <v>46064.975982731485</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46196.78475478009</v>
+      </c>
       <c r="D12" s="5">
-        <v>46160.68348146991</v>
+        <v>46196.78475805555</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -5228,7 +5230,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46155.82960403935</v>
+        <v>46196.78476547454</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5289,7 +5291,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46154.59706932871</v>
+        <v>46196.78476415509</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46126.79216469907</v>
+        <v>46197.58388252315</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5228,9 +5228,11 @@
       <c r="B66" s="5">
         <v>46064.9759750463</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46197.5838743287</v>
+      </c>
       <c r="D66" s="5">
-        <v>46196.78476547454</v>
+        <v>46197.583876261575</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5291,7 +5293,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46196.78476415509</v>
+        <v>46197.58388143519</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -1450,13 +1450,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46064.97598012732</v>
+        <v>46064.809313460646</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.73975011574</v>
+        <v>46092.573083449075</v>
       </c>
       <c r="D4" s="5">
-        <v>46127.58667684028</v>
+        <v>46127.420010173606</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1499,13 +1499,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46064.97598055555</v>
+        <v>46064.80931388889</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.739719942125</v>
+        <v>46092.57305327547</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.739750775465</v>
+        <v>46092.57308410879</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1564,13 +1564,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46064.97598087963</v>
+        <v>46064.809314212966</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.7397205787</v>
+        <v>46092.57305391204</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.73975069444</v>
+        <v>46092.57308402778</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1629,13 +1629,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46064.975981192125</v>
+        <v>46064.80931452547</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.739721018515</v>
+        <v>46092.57305435185</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.739751354165</v>
+        <v>46092.5730846875</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1694,13 +1694,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46064.9759815162</v>
+        <v>46064.80931484954</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.73972149305</v>
+        <v>46092.57305482639</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.79292365741</v>
+        <v>46100.62625699074</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1759,13 +1759,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46064.97598181713</v>
+        <v>46064.80931515046</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.73972216435</v>
+        <v>46092.57305549768</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.73975703704</v>
+        <v>46092.573090370366</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1824,11 +1824,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46064.97598212963</v>
+        <v>46064.80931546296</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46196.784762916664</v>
+        <v>46196.61809625</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1871,13 +1871,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46064.97598241898</v>
+        <v>46064.80931575231</v>
       </c>
       <c r="C11" s="8">
-        <v>46112.65081634259</v>
+        <v>46112.484149675925</v>
       </c>
       <c r="D11" s="8">
-        <v>46112.65084314815</v>
+        <v>46112.48417648148</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1936,13 +1936,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46064.975982731485</v>
+        <v>46064.80931606481</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.78475478009</v>
+        <v>46196.61808811342</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.78475805555</v>
+        <v>46196.61809138889</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2001,13 +2001,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46064.975983020835</v>
+        <v>46064.80931635416</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51367688658</v>
+        <v>46114.347010219906</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.51369047454</v>
+        <v>46114.34702380787</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2054,13 +2054,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46064.97597363426</v>
+        <v>46064.809306967596</v>
       </c>
       <c r="C14" s="5">
-        <v>46111.78998141203</v>
+        <v>46111.623314745375</v>
       </c>
       <c r="D14" s="5">
-        <v>46111.78998364584</v>
+        <v>46111.62331697917</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2119,13 +2119,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46064.975974270834</v>
+        <v>46064.80930760417</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.78999103009</v>
+        <v>46111.62332436343</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.78999260417</v>
+        <v>46111.6233259375</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2184,13 +2184,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46064.975974560184</v>
+        <v>46064.80930789352</v>
       </c>
       <c r="C16" s="5">
-        <v>46111.79000237268</v>
+        <v>46111.62333570602</v>
       </c>
       <c r="D16" s="5">
-        <v>46111.790004016206</v>
+        <v>46111.623337349534</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2249,13 +2249,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46064.97597482639</v>
+        <v>46064.80930815972</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.51365946759</v>
+        <v>46114.34699280093</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51367697917</v>
+        <v>46114.3470103125</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2314,13 +2314,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46064.97597510417</v>
+        <v>46064.8093084375</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.65099793981</v>
+        <v>46112.48433127315</v>
       </c>
       <c r="D18" s="5">
-        <v>46139.78176002315</v>
+        <v>46139.61509335648</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2363,13 +2363,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46064.97597564815</v>
+        <v>46064.80930898148</v>
       </c>
       <c r="C19" s="8">
-        <v>46111.79006763889</v>
+        <v>46111.623400972225</v>
       </c>
       <c r="D19" s="8">
-        <v>46111.79008209491</v>
+        <v>46111.62341542824</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2428,13 +2428,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46064.97597537037</v>
+        <v>46064.809308703705</v>
       </c>
       <c r="C20" s="5">
-        <v>46111.79007887731</v>
+        <v>46111.62341221065</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.79009476852</v>
+        <v>46111.623428101855</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -2493,13 +2493,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46064.97597590278</v>
+        <v>46064.80930923611</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.6509687037</v>
+        <v>46112.48430203703</v>
       </c>
       <c r="D21" s="8">
-        <v>46112.65100008102</v>
+        <v>46112.48433341435</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2558,13 +2558,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46064.97597616898</v>
+        <v>46064.809309502314</v>
       </c>
       <c r="C22" s="5">
-        <v>46111.79010834491</v>
+        <v>46111.62344167824</v>
       </c>
       <c r="D22" s="5">
-        <v>46111.79012521991</v>
+        <v>46111.62345855324</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2623,13 +2623,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46064.975973125</v>
+        <v>46064.80930645834</v>
       </c>
       <c r="C23" s="8">
-        <v>46111.790157511576</v>
+        <v>46111.62349084491</v>
       </c>
       <c r="D23" s="8">
-        <v>46111.79017418981</v>
+        <v>46111.62350752315</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2688,13 +2688,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46064.97597337963</v>
+        <v>46064.80930671297</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.76428164352</v>
+        <v>46114.597614976854</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.82944616898</v>
+        <v>46155.662779502316</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2737,13 +2737,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46064.97597363426</v>
+        <v>46064.809306967596</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.79079113426</v>
+        <v>46111.62412446759</v>
       </c>
       <c r="D25" s="8">
-        <v>46139.781813090274</v>
+        <v>46139.61514642361</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2802,13 +2802,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46064.98709253472</v>
+        <v>46064.820425868056</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.79073707176</v>
+        <v>46111.624070405094</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.79073866898</v>
+        <v>46111.62407200232</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2857,13 +2857,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46064.98694590278</v>
+        <v>46064.82027923611</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.79077587963</v>
+        <v>46111.624109212964</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.790777268514</v>
+        <v>46111.62411060186</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2912,13 +2912,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46064.975974479166</v>
+        <v>46064.809307812495</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.829439340276</v>
+        <v>46155.66277267361</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.82950846065</v>
+        <v>46155.66284179398</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2977,13 +2977,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46064.97597476852</v>
+        <v>46064.80930810185</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.651014675925</v>
+        <v>46112.48434800926</v>
       </c>
       <c r="D29" s="8">
-        <v>46112.651016296295</v>
+        <v>46112.48434962963</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3038,13 +3038,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46064.975975023146</v>
+        <v>46064.80930835648</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.55801283565</v>
+        <v>46154.39134616898</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.558014236114</v>
+        <v>46154.39134756944</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3099,13 +3099,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46064.97597528935</v>
+        <v>46064.80930862269</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.79065659722</v>
+        <v>46111.62398993055</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.79066731481</v>
+        <v>46111.62400064815</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3164,13 +3164,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46064.97597284723</v>
+        <v>46064.809306180556</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.79059375</v>
+        <v>46111.62392708333</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.790595659724</v>
+        <v>46111.62392899305</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3225,13 +3225,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46064.97597324074</v>
+        <v>46064.809306574076</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.79063767361</v>
+        <v>46111.62397100695</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.79063912037</v>
+        <v>46111.6239724537</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3286,13 +3286,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46064.975973506946</v>
+        <v>46064.80930684028</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.79054489583</v>
+        <v>46111.62387822916</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.79055864584</v>
+        <v>46111.623891979165</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3351,13 +3351,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46064.97597377315</v>
+        <v>46064.80930710648</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.790480682874</v>
+        <v>46111.6238140162</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.79048188658</v>
+        <v>46111.62381521991</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3412,13 +3412,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46064.975974050925</v>
+        <v>46064.80930738426</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.79051731482</v>
+        <v>46111.623850648146</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.79051883102</v>
+        <v>46111.62385216435</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3473,13 +3473,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46064.97597431713</v>
+        <v>46064.80930765046</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.79052896991</v>
+        <v>46111.62386230324</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.79053048611</v>
+        <v>46111.62386381945</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3534,13 +3534,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46064.97597459491</v>
+        <v>46064.80930792824</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.79043043981</v>
+        <v>46111.62376377315</v>
       </c>
       <c r="D38" s="5">
-        <v>46139.78184163195</v>
+        <v>46139.61517496528</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3599,13 +3599,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46064.97597487269</v>
+        <v>46064.80930820602</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.79036834491</v>
+        <v>46111.62370167824</v>
       </c>
       <c r="D39" s="8">
-        <v>46111.79036971065</v>
+        <v>46111.62370304398</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3660,13 +3660,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46064.97597515046</v>
+        <v>46064.8093084838</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.790416261574</v>
+        <v>46111.6237495949</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.79041780093</v>
+        <v>46111.62375113426</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3721,13 +3721,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46064.97597454861</v>
+        <v>46064.809307881944</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.768620312505</v>
+        <v>46114.60195364583</v>
       </c>
       <c r="D41" s="8">
-        <v>46139.781639733796</v>
+        <v>46139.61497306713</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3770,13 +3770,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.66955917824</v>
+        <v>46070.50289251158</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.513817430554</v>
+        <v>46114.34715076389</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.51383626157</v>
+        <v>46114.34716959491</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3835,13 +3835,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46064.97597483796</v>
+        <v>46064.8093081713</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.51387333333</v>
+        <v>46114.347206666665</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.513888587964</v>
+        <v>46114.3472219213</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3900,13 +3900,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46087.50355304398</v>
+        <v>46087.336886377314</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.513921412035</v>
+        <v>46114.34725474537</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.51393545139</v>
+        <v>46114.347268784724</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3965,13 +3965,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46087.50359630787</v>
+        <v>46087.3369296412</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.768603275465</v>
+        <v>46114.6019366088</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.181483541666</v>
+        <v>46127.014816875</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4028,13 +4028,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46064.97597513889</v>
+        <v>46064.80930847222</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.71552679398</v>
+        <v>46107.54886012731</v>
       </c>
       <c r="D46" s="5">
-        <v>46139.7815396875</v>
+        <v>46139.61487302084</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4077,13 +4077,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46064.97597543981</v>
+        <v>46064.80930877315</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.71551097222</v>
+        <v>46107.54884430555</v>
       </c>
       <c r="D47" s="8">
-        <v>46139.78147785879</v>
+        <v>46139.61481119213</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4142,13 +4142,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46064.97597572916</v>
+        <v>46064.809309062504</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.71543211806</v>
+        <v>46107.548765451385</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.78149715278</v>
+        <v>46139.61483048611</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4207,13 +4207,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46064.975976030095</v>
+        <v>46064.80930936342</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.71566543981</v>
+        <v>46107.54899877315</v>
       </c>
       <c r="D49" s="8">
-        <v>46139.781448344904</v>
+        <v>46139.61478167824</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4256,13 +4256,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46064.975976319445</v>
+        <v>46064.809309652774</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.71520322916</v>
+        <v>46107.5485365625</v>
       </c>
       <c r="D50" s="5">
-        <v>46139.78134862268</v>
+        <v>46139.61468195602</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4321,13 +4321,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46064.97597666667</v>
+        <v>46064.80931</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.71531623843</v>
+        <v>46107.54864957176</v>
       </c>
       <c r="D51" s="8">
-        <v>46139.7813684838</v>
+        <v>46139.61470181713</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4386,13 +4386,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46064.9759734838</v>
+        <v>46064.80930681713</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.71564938658</v>
+        <v>46107.548982719905</v>
       </c>
       <c r="D52" s="5">
-        <v>46139.781402106484</v>
+        <v>46139.61473543981</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4449,13 +4449,13 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46064.975973865745</v>
+        <v>46064.80930719907</v>
       </c>
       <c r="C53" s="8">
-        <v>46155.82935329861</v>
+        <v>46155.66268663194</v>
       </c>
       <c r="D53" s="8">
-        <v>46155.82935478009</v>
+        <v>46155.66268811343</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4498,13 +4498,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46064.97597451389</v>
+        <v>46064.80930784722</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.71485509259</v>
+        <v>46107.54818842592</v>
       </c>
       <c r="D54" s="5">
-        <v>46139.7811046412</v>
+        <v>46139.61443797454</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4561,13 +4561,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46064.97597511574</v>
+        <v>46064.809308449076</v>
       </c>
       <c r="C55" s="8">
-        <v>46154.558066516205</v>
+        <v>46154.39139984954</v>
       </c>
       <c r="D55" s="8">
-        <v>46155.82954369213</v>
+        <v>46155.66287702546</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>56</v>
@@ -4624,13 +4624,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46064.97597422454</v>
+        <v>46064.809307557865</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.71470586806</v>
+        <v>46107.548039201385</v>
       </c>
       <c r="D56" s="5">
-        <v>46139.78107806713</v>
+        <v>46139.614411400464</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4687,13 +4687,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.50497587963</v>
+        <v>46065.338309212966</v>
       </c>
       <c r="C57" s="8">
-        <v>46107.714572083336</v>
+        <v>46107.547905416664</v>
       </c>
       <c r="D57" s="8">
-        <v>46139.78105626158</v>
+        <v>46139.614389594906</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4750,13 +4750,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46064.97597565972</v>
+        <v>46064.809308993055</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.71504505787</v>
+        <v>46107.548378391206</v>
       </c>
       <c r="D58" s="5">
-        <v>46139.78125670139</v>
+        <v>46139.61459003472</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4799,13 +4799,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46064.975975925925</v>
+        <v>46064.80930925926</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.71502270833</v>
+        <v>46107.54835604166</v>
       </c>
       <c r="D59" s="8">
-        <v>46120.17345672454</v>
+        <v>46120.00679005787</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4864,13 +4864,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46064.97597623843</v>
+        <v>46064.80930957176</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.7136993287</v>
+        <v>46107.54703266204</v>
       </c>
       <c r="D60" s="5">
-        <v>46139.781139259256</v>
+        <v>46139.61447259259</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -4927,13 +4927,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46064.9759734375</v>
+        <v>46064.80930677083</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.713914548614</v>
+        <v>46107.54724788194</v>
       </c>
       <c r="D61" s="8">
-        <v>46139.78116083333</v>
+        <v>46139.61449416667</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>222</v>
@@ -4990,13 +4990,13 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46064.97597377315</v>
+        <v>46064.80930710648</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.71404958333</v>
+        <v>46107.547382916666</v>
       </c>
       <c r="D62" s="5">
-        <v>46139.78118356482</v>
+        <v>46139.614516898146</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5053,13 +5053,13 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46064.97597429398</v>
+        <v>46064.809307627314</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.71416802083</v>
+        <v>46107.547501354165</v>
       </c>
       <c r="D63" s="8">
-        <v>46126.207354363425</v>
+        <v>46126.04068769676</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5116,13 +5116,13 @@
         <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46064.97597454861</v>
+        <v>46064.809307881944</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.71432141204</v>
+        <v>46107.54765474537</v>
       </c>
       <c r="D64" s="5">
-        <v>46139.78120690973</v>
+        <v>46139.614540243056</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5179,11 +5179,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46064.97597479167</v>
+        <v>46064.809308125</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.58388252315</v>
+        <v>46197.417215856476</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5226,13 +5226,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46064.9759750463</v>
+        <v>46064.80930837963</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.5838743287</v>
+        <v>46197.41720766204</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.583876261575</v>
+        <v>46197.4172095949</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5289,11 +5289,11 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46064.97597528935</v>
+        <v>46064.80930862269</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46197.58388143519</v>
+        <v>46197.41721476852</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5350,11 +5350,11 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46064.975975532405</v>
+        <v>46064.80930886574</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46139.168115381945</v>
+        <v>46139.00144871528</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5411,11 +5411,11 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46064.975975787034</v>
+        <v>46064.80930912037</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46140.16795534722</v>
+        <v>46140.001288680556</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>251</v>
@@ -5472,11 +5472,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46064.97597357639</v>
+        <v>46064.80930690972</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.792140254634</v>
+        <v>46126.62547358796</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>254</v>
@@ -5519,11 +5519,11 @@
         <v>256</v>
       </c>
       <c r="B71" s="8">
-        <v>46064.97597436343</v>
+        <v>46064.80930769676</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46150.168567719906</v>
+        <v>46150.00190105324</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>257</v>
@@ -5582,11 +5582,11 @@
         <v>260</v>
       </c>
       <c r="B72" s="5">
-        <v>46064.975974050925</v>
+        <v>46064.80930738426</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46150.16856546296</v>
+        <v>46150.0018987963</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>261</v>
@@ -5645,11 +5645,11 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.53176077546</v>
+        <v>46090.3650941088</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46126.792140405094</v>
+        <v>46126.62547373843</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5692,11 +5692,11 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.53365568287</v>
+        <v>46090.366989016205</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46149.168085868056</v>
+        <v>46149.00141920139</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5755,11 +5755,11 @@
         <v>269</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.53385733796</v>
+        <v>46090.3671906713</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46161.167864664356</v>
+        <v>46161.001197997684</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>270</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -1450,13 +1450,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46064.809313460646</v>
+        <v>46064.97598012732</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.573083449075</v>
+        <v>46092.73975011574</v>
       </c>
       <c r="D4" s="5">
-        <v>46127.420010173606</v>
+        <v>46127.58667684028</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1499,13 +1499,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46064.80931388889</v>
+        <v>46064.97598055555</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.57305327547</v>
+        <v>46092.739719942125</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.57308410879</v>
+        <v>46092.739750775465</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1564,13 +1564,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46064.809314212966</v>
+        <v>46064.97598087963</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.57305391204</v>
+        <v>46092.7397205787</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.57308402778</v>
+        <v>46092.73975069444</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1629,13 +1629,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46064.80931452547</v>
+        <v>46064.975981192125</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.57305435185</v>
+        <v>46092.739721018515</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.5730846875</v>
+        <v>46092.739751354165</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1694,13 +1694,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46064.80931484954</v>
+        <v>46064.9759815162</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.57305482639</v>
+        <v>46092.73972149305</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.62625699074</v>
+        <v>46100.79292365741</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1759,13 +1759,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46064.80931515046</v>
+        <v>46064.97598181713</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.57305549768</v>
+        <v>46092.73972216435</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.573090370366</v>
+        <v>46092.73975703704</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1824,11 +1824,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46064.80931546296</v>
+        <v>46064.97598212963</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46196.61809625</v>
+        <v>46196.784762916664</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1871,13 +1871,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46064.80931575231</v>
+        <v>46064.97598241898</v>
       </c>
       <c r="C11" s="8">
-        <v>46112.484149675925</v>
+        <v>46112.65081634259</v>
       </c>
       <c r="D11" s="8">
-        <v>46112.48417648148</v>
+        <v>46112.65084314815</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1936,13 +1936,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46064.80931606481</v>
+        <v>46064.975982731485</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.61808811342</v>
+        <v>46196.78475478009</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.61809138889</v>
+        <v>46196.78475805555</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2001,13 +2001,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46064.80931635416</v>
+        <v>46064.975983020835</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.347010219906</v>
+        <v>46114.51367688658</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.34702380787</v>
+        <v>46114.51369047454</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2054,13 +2054,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46064.809306967596</v>
+        <v>46064.97597363426</v>
       </c>
       <c r="C14" s="5">
-        <v>46111.623314745375</v>
+        <v>46111.78998141203</v>
       </c>
       <c r="D14" s="5">
-        <v>46111.62331697917</v>
+        <v>46111.78998364584</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2119,13 +2119,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46064.80930760417</v>
+        <v>46064.975974270834</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.62332436343</v>
+        <v>46111.78999103009</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.6233259375</v>
+        <v>46111.78999260417</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2184,13 +2184,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46064.80930789352</v>
+        <v>46064.975974560184</v>
       </c>
       <c r="C16" s="5">
-        <v>46111.62333570602</v>
+        <v>46111.79000237268</v>
       </c>
       <c r="D16" s="5">
-        <v>46111.623337349534</v>
+        <v>46111.790004016206</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2249,13 +2249,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46064.80930815972</v>
+        <v>46064.97597482639</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34699280093</v>
+        <v>46114.51365946759</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.3470103125</v>
+        <v>46114.51367697917</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2314,13 +2314,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46064.8093084375</v>
+        <v>46064.97597510417</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.48433127315</v>
+        <v>46112.65099793981</v>
       </c>
       <c r="D18" s="5">
-        <v>46139.61509335648</v>
+        <v>46139.78176002315</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2363,13 +2363,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46064.80930898148</v>
+        <v>46064.97597564815</v>
       </c>
       <c r="C19" s="8">
-        <v>46111.623400972225</v>
+        <v>46111.79006763889</v>
       </c>
       <c r="D19" s="8">
-        <v>46111.62341542824</v>
+        <v>46111.79008209491</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2428,13 +2428,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46064.809308703705</v>
+        <v>46064.97597537037</v>
       </c>
       <c r="C20" s="5">
-        <v>46111.62341221065</v>
+        <v>46111.79007887731</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.623428101855</v>
+        <v>46111.79009476852</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -2493,13 +2493,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46064.80930923611</v>
+        <v>46064.97597590278</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.48430203703</v>
+        <v>46112.6509687037</v>
       </c>
       <c r="D21" s="8">
-        <v>46112.48433341435</v>
+        <v>46112.65100008102</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2558,13 +2558,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46064.809309502314</v>
+        <v>46064.97597616898</v>
       </c>
       <c r="C22" s="5">
-        <v>46111.62344167824</v>
+        <v>46111.79010834491</v>
       </c>
       <c r="D22" s="5">
-        <v>46111.62345855324</v>
+        <v>46111.79012521991</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2623,13 +2623,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46064.80930645834</v>
+        <v>46064.975973125</v>
       </c>
       <c r="C23" s="8">
-        <v>46111.62349084491</v>
+        <v>46111.790157511576</v>
       </c>
       <c r="D23" s="8">
-        <v>46111.62350752315</v>
+        <v>46111.79017418981</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2688,13 +2688,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46064.80930671297</v>
+        <v>46064.97597337963</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.597614976854</v>
+        <v>46114.76428164352</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.662779502316</v>
+        <v>46155.82944616898</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2737,13 +2737,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46064.809306967596</v>
+        <v>46064.97597363426</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.62412446759</v>
+        <v>46111.79079113426</v>
       </c>
       <c r="D25" s="8">
-        <v>46139.61514642361</v>
+        <v>46139.781813090274</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2802,13 +2802,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46064.820425868056</v>
+        <v>46064.98709253472</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.624070405094</v>
+        <v>46111.79073707176</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.62407200232</v>
+        <v>46111.79073866898</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2857,13 +2857,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46064.82027923611</v>
+        <v>46064.98694590278</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.624109212964</v>
+        <v>46111.79077587963</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.62411060186</v>
+        <v>46111.790777268514</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2912,13 +2912,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46064.809307812495</v>
+        <v>46064.975974479166</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.66277267361</v>
+        <v>46155.829439340276</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.66284179398</v>
+        <v>46155.82950846065</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2977,13 +2977,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46064.80930810185</v>
+        <v>46064.97597476852</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.48434800926</v>
+        <v>46112.651014675925</v>
       </c>
       <c r="D29" s="8">
-        <v>46112.48434962963</v>
+        <v>46112.651016296295</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3038,13 +3038,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46064.80930835648</v>
+        <v>46064.975975023146</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.39134616898</v>
+        <v>46154.55801283565</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.39134756944</v>
+        <v>46154.558014236114</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3099,13 +3099,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46064.80930862269</v>
+        <v>46064.97597528935</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.62398993055</v>
+        <v>46111.79065659722</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.62400064815</v>
+        <v>46111.79066731481</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3164,13 +3164,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46064.809306180556</v>
+        <v>46064.97597284723</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.62392708333</v>
+        <v>46111.79059375</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.62392899305</v>
+        <v>46111.790595659724</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3225,13 +3225,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46064.809306574076</v>
+        <v>46064.97597324074</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.62397100695</v>
+        <v>46111.79063767361</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.6239724537</v>
+        <v>46111.79063912037</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3286,13 +3286,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46064.80930684028</v>
+        <v>46064.975973506946</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.62387822916</v>
+        <v>46111.79054489583</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.623891979165</v>
+        <v>46111.79055864584</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3351,13 +3351,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46064.80930710648</v>
+        <v>46064.97597377315</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.6238140162</v>
+        <v>46111.790480682874</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.62381521991</v>
+        <v>46111.79048188658</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3412,13 +3412,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46064.80930738426</v>
+        <v>46064.975974050925</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.623850648146</v>
+        <v>46111.79051731482</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.62385216435</v>
+        <v>46111.79051883102</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3473,13 +3473,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46064.80930765046</v>
+        <v>46064.97597431713</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.62386230324</v>
+        <v>46111.79052896991</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.62386381945</v>
+        <v>46111.79053048611</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3534,13 +3534,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46064.80930792824</v>
+        <v>46064.97597459491</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.62376377315</v>
+        <v>46111.79043043981</v>
       </c>
       <c r="D38" s="5">
-        <v>46139.61517496528</v>
+        <v>46139.78184163195</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3599,13 +3599,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46064.80930820602</v>
+        <v>46064.97597487269</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.62370167824</v>
+        <v>46111.79036834491</v>
       </c>
       <c r="D39" s="8">
-        <v>46111.62370304398</v>
+        <v>46111.79036971065</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3660,13 +3660,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46064.8093084838</v>
+        <v>46064.97597515046</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.6237495949</v>
+        <v>46111.790416261574</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.62375113426</v>
+        <v>46111.79041780093</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3721,13 +3721,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46064.809307881944</v>
+        <v>46064.97597454861</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.60195364583</v>
+        <v>46114.768620312505</v>
       </c>
       <c r="D41" s="8">
-        <v>46139.61497306713</v>
+        <v>46139.781639733796</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3770,13 +3770,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.50289251158</v>
+        <v>46070.66955917824</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.34715076389</v>
+        <v>46114.513817430554</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.34716959491</v>
+        <v>46114.51383626157</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3835,13 +3835,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46064.8093081713</v>
+        <v>46064.97597483796</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.347206666665</v>
+        <v>46114.51387333333</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.3472219213</v>
+        <v>46114.513888587964</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3900,13 +3900,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46087.336886377314</v>
+        <v>46087.50355304398</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.34725474537</v>
+        <v>46114.513921412035</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.347268784724</v>
+        <v>46114.51393545139</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3965,13 +3965,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46087.3369296412</v>
+        <v>46087.50359630787</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.6019366088</v>
+        <v>46114.768603275465</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.014816875</v>
+        <v>46127.181483541666</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4028,13 +4028,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46064.80930847222</v>
+        <v>46064.97597513889</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.54886012731</v>
+        <v>46107.71552679398</v>
       </c>
       <c r="D46" s="5">
-        <v>46139.61487302084</v>
+        <v>46139.7815396875</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4077,13 +4077,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46064.80930877315</v>
+        <v>46064.97597543981</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.54884430555</v>
+        <v>46107.71551097222</v>
       </c>
       <c r="D47" s="8">
-        <v>46139.61481119213</v>
+        <v>46139.78147785879</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4142,13 +4142,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46064.809309062504</v>
+        <v>46064.97597572916</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.548765451385</v>
+        <v>46107.71543211806</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.61483048611</v>
+        <v>46139.78149715278</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4207,13 +4207,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46064.80930936342</v>
+        <v>46064.975976030095</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.54899877315</v>
+        <v>46107.71566543981</v>
       </c>
       <c r="D49" s="8">
-        <v>46139.61478167824</v>
+        <v>46139.781448344904</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4256,13 +4256,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46064.809309652774</v>
+        <v>46064.975976319445</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.5485365625</v>
+        <v>46107.71520322916</v>
       </c>
       <c r="D50" s="5">
-        <v>46139.61468195602</v>
+        <v>46139.78134862268</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4321,13 +4321,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46064.80931</v>
+        <v>46064.97597666667</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.54864957176</v>
+        <v>46107.71531623843</v>
       </c>
       <c r="D51" s="8">
-        <v>46139.61470181713</v>
+        <v>46139.7813684838</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4386,13 +4386,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46064.80930681713</v>
+        <v>46064.9759734838</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.548982719905</v>
+        <v>46107.71564938658</v>
       </c>
       <c r="D52" s="5">
-        <v>46139.61473543981</v>
+        <v>46139.781402106484</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4449,13 +4449,13 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46064.80930719907</v>
+        <v>46064.975973865745</v>
       </c>
       <c r="C53" s="8">
-        <v>46155.66268663194</v>
+        <v>46155.82935329861</v>
       </c>
       <c r="D53" s="8">
-        <v>46155.66268811343</v>
+        <v>46155.82935478009</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4498,13 +4498,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46064.80930784722</v>
+        <v>46064.97597451389</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.54818842592</v>
+        <v>46107.71485509259</v>
       </c>
       <c r="D54" s="5">
-        <v>46139.61443797454</v>
+        <v>46139.7811046412</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4561,13 +4561,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46064.809308449076</v>
+        <v>46064.97597511574</v>
       </c>
       <c r="C55" s="8">
-        <v>46154.39139984954</v>
+        <v>46154.558066516205</v>
       </c>
       <c r="D55" s="8">
-        <v>46155.66287702546</v>
+        <v>46155.82954369213</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>56</v>
@@ -4624,13 +4624,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46064.809307557865</v>
+        <v>46064.97597422454</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.548039201385</v>
+        <v>46107.71470586806</v>
       </c>
       <c r="D56" s="5">
-        <v>46139.614411400464</v>
+        <v>46139.78107806713</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4687,13 +4687,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.338309212966</v>
+        <v>46065.50497587963</v>
       </c>
       <c r="C57" s="8">
-        <v>46107.547905416664</v>
+        <v>46107.714572083336</v>
       </c>
       <c r="D57" s="8">
-        <v>46139.614389594906</v>
+        <v>46139.78105626158</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4750,13 +4750,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46064.809308993055</v>
+        <v>46064.97597565972</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.548378391206</v>
+        <v>46107.71504505787</v>
       </c>
       <c r="D58" s="5">
-        <v>46139.61459003472</v>
+        <v>46139.78125670139</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4799,13 +4799,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46064.80930925926</v>
+        <v>46064.975975925925</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.54835604166</v>
+        <v>46107.71502270833</v>
       </c>
       <c r="D59" s="8">
-        <v>46120.00679005787</v>
+        <v>46120.17345672454</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4864,13 +4864,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46064.80930957176</v>
+        <v>46064.97597623843</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.54703266204</v>
+        <v>46107.7136993287</v>
       </c>
       <c r="D60" s="5">
-        <v>46139.61447259259</v>
+        <v>46139.781139259256</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -4927,13 +4927,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46064.80930677083</v>
+        <v>46064.9759734375</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.54724788194</v>
+        <v>46107.713914548614</v>
       </c>
       <c r="D61" s="8">
-        <v>46139.61449416667</v>
+        <v>46139.78116083333</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>222</v>
@@ -4990,13 +4990,13 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46064.80930710648</v>
+        <v>46064.97597377315</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.547382916666</v>
+        <v>46107.71404958333</v>
       </c>
       <c r="D62" s="5">
-        <v>46139.614516898146</v>
+        <v>46139.78118356482</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5053,13 +5053,13 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46064.809307627314</v>
+        <v>46064.97597429398</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.547501354165</v>
+        <v>46107.71416802083</v>
       </c>
       <c r="D63" s="8">
-        <v>46126.04068769676</v>
+        <v>46126.207354363425</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5116,13 +5116,13 @@
         <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46064.809307881944</v>
+        <v>46064.97597454861</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.54765474537</v>
+        <v>46107.71432141204</v>
       </c>
       <c r="D64" s="5">
-        <v>46139.614540243056</v>
+        <v>46139.78120690973</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5179,11 +5179,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46064.809308125</v>
+        <v>46064.97597479167</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.417215856476</v>
+        <v>46197.71022986111</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5226,13 +5226,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46064.80930837963</v>
+        <v>46064.9759750463</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.41720766204</v>
+        <v>46197.5838743287</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.4172095949</v>
+        <v>46197.583876261575</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5289,11 +5289,13 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46064.80930862269</v>
-      </c>
-      <c r="C67" s="9"/>
+        <v>46064.97597528935</v>
+      </c>
+      <c r="C67" s="8">
+        <v>46197.71009467593</v>
+      </c>
       <c r="D67" s="8">
-        <v>46197.41721476852</v>
+        <v>46197.71009662037</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5350,11 +5352,13 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46064.80930886574</v>
-      </c>
-      <c r="C68" s="6"/>
+        <v>46064.975975532405</v>
+      </c>
+      <c r="C68" s="5">
+        <v>46197.71018288194</v>
+      </c>
       <c r="D68" s="5">
-        <v>46139.00144871528</v>
+        <v>46197.71018483797</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5411,11 +5415,13 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46064.80930912037</v>
-      </c>
-      <c r="C69" s="9"/>
+        <v>46064.975975787034</v>
+      </c>
+      <c r="C69" s="8">
+        <v>46197.71022226852</v>
+      </c>
       <c r="D69" s="8">
-        <v>46140.001288680556</v>
+        <v>46197.71049135417</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>251</v>
@@ -5472,11 +5478,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46064.80930690972</v>
+        <v>46064.97597357639</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.62547358796</v>
+        <v>46126.792140254634</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>254</v>
@@ -5519,11 +5525,11 @@
         <v>256</v>
       </c>
       <c r="B71" s="8">
-        <v>46064.80930769676</v>
+        <v>46064.97597436343</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46150.00190105324</v>
+        <v>46197.71023167824</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>257</v>
@@ -5582,11 +5588,11 @@
         <v>260</v>
       </c>
       <c r="B72" s="5">
-        <v>46064.80930738426</v>
+        <v>46064.975974050925</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46150.0018987963</v>
+        <v>46197.710233125</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>261</v>
@@ -5645,11 +5651,11 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.3650941088</v>
+        <v>46090.53176077546</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46126.62547373843</v>
+        <v>46126.792140405094</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5692,11 +5698,11 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.366989016205</v>
+        <v>46090.53365568287</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46149.00141920139</v>
+        <v>46197.71023440972</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5755,11 +5761,11 @@
         <v>269</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.3671906713</v>
+        <v>46090.53385733796</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46161.001197997684</v>
+        <v>46161.167864664356</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>270</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -1450,13 +1450,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46064.97598012732</v>
+        <v>46064.809313460646</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.73975011574</v>
+        <v>46092.573083449075</v>
       </c>
       <c r="D4" s="5">
-        <v>46127.58667684028</v>
+        <v>46127.420010173606</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1499,13 +1499,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46064.97598055555</v>
+        <v>46064.80931388889</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.739719942125</v>
+        <v>46092.57305327547</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.739750775465</v>
+        <v>46092.57308410879</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1564,13 +1564,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46064.97598087963</v>
+        <v>46064.809314212966</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.7397205787</v>
+        <v>46092.57305391204</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.73975069444</v>
+        <v>46092.57308402778</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1629,13 +1629,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46064.975981192125</v>
+        <v>46064.80931452547</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.739721018515</v>
+        <v>46092.57305435185</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.739751354165</v>
+        <v>46092.5730846875</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1694,13 +1694,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46064.9759815162</v>
+        <v>46064.80931484954</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.73972149305</v>
+        <v>46092.57305482639</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.79292365741</v>
+        <v>46100.62625699074</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1759,13 +1759,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46064.97598181713</v>
+        <v>46064.80931515046</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.73972216435</v>
+        <v>46092.57305549768</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.73975703704</v>
+        <v>46092.573090370366</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1824,11 +1824,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46064.97598212963</v>
+        <v>46064.80931546296</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46196.784762916664</v>
+        <v>46196.61809625</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1871,13 +1871,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46064.97598241898</v>
+        <v>46064.80931575231</v>
       </c>
       <c r="C11" s="8">
-        <v>46112.65081634259</v>
+        <v>46112.484149675925</v>
       </c>
       <c r="D11" s="8">
-        <v>46112.65084314815</v>
+        <v>46112.48417648148</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1936,13 +1936,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46064.975982731485</v>
+        <v>46064.80931606481</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.78475478009</v>
+        <v>46196.61808811342</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.78475805555</v>
+        <v>46196.61809138889</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2001,13 +2001,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46064.975983020835</v>
+        <v>46064.80931635416</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51367688658</v>
+        <v>46114.347010219906</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.51369047454</v>
+        <v>46114.34702380787</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2054,13 +2054,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46064.97597363426</v>
+        <v>46064.809306967596</v>
       </c>
       <c r="C14" s="5">
-        <v>46111.78998141203</v>
+        <v>46111.623314745375</v>
       </c>
       <c r="D14" s="5">
-        <v>46111.78998364584</v>
+        <v>46111.62331697917</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2119,13 +2119,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46064.975974270834</v>
+        <v>46064.80930760417</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.78999103009</v>
+        <v>46111.62332436343</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.78999260417</v>
+        <v>46111.6233259375</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2184,13 +2184,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46064.975974560184</v>
+        <v>46064.80930789352</v>
       </c>
       <c r="C16" s="5">
-        <v>46111.79000237268</v>
+        <v>46111.62333570602</v>
       </c>
       <c r="D16" s="5">
-        <v>46111.790004016206</v>
+        <v>46111.623337349534</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2249,13 +2249,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46064.97597482639</v>
+        <v>46064.80930815972</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.51365946759</v>
+        <v>46114.34699280093</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51367697917</v>
+        <v>46114.3470103125</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2314,13 +2314,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46064.97597510417</v>
+        <v>46064.8093084375</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.65099793981</v>
+        <v>46112.48433127315</v>
       </c>
       <c r="D18" s="5">
-        <v>46139.78176002315</v>
+        <v>46139.61509335648</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2363,13 +2363,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46064.97597564815</v>
+        <v>46064.80930898148</v>
       </c>
       <c r="C19" s="8">
-        <v>46111.79006763889</v>
+        <v>46111.623400972225</v>
       </c>
       <c r="D19" s="8">
-        <v>46111.79008209491</v>
+        <v>46111.62341542824</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2428,13 +2428,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46064.97597537037</v>
+        <v>46064.809308703705</v>
       </c>
       <c r="C20" s="5">
-        <v>46111.79007887731</v>
+        <v>46111.62341221065</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.79009476852</v>
+        <v>46111.623428101855</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -2493,13 +2493,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46064.97597590278</v>
+        <v>46064.80930923611</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.6509687037</v>
+        <v>46112.48430203703</v>
       </c>
       <c r="D21" s="8">
-        <v>46112.65100008102</v>
+        <v>46112.48433341435</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2558,13 +2558,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46064.97597616898</v>
+        <v>46064.809309502314</v>
       </c>
       <c r="C22" s="5">
-        <v>46111.79010834491</v>
+        <v>46111.62344167824</v>
       </c>
       <c r="D22" s="5">
-        <v>46111.79012521991</v>
+        <v>46111.62345855324</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2623,13 +2623,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46064.975973125</v>
+        <v>46064.80930645834</v>
       </c>
       <c r="C23" s="8">
-        <v>46111.790157511576</v>
+        <v>46111.62349084491</v>
       </c>
       <c r="D23" s="8">
-        <v>46111.79017418981</v>
+        <v>46111.62350752315</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2688,13 +2688,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46064.97597337963</v>
+        <v>46064.80930671297</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.76428164352</v>
+        <v>46114.597614976854</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.82944616898</v>
+        <v>46155.662779502316</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2737,13 +2737,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46064.97597363426</v>
+        <v>46064.809306967596</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.79079113426</v>
+        <v>46111.62412446759</v>
       </c>
       <c r="D25" s="8">
-        <v>46139.781813090274</v>
+        <v>46139.61514642361</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2802,13 +2802,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46064.98709253472</v>
+        <v>46064.820425868056</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.79073707176</v>
+        <v>46111.624070405094</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.79073866898</v>
+        <v>46111.62407200232</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2857,13 +2857,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46064.98694590278</v>
+        <v>46064.82027923611</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.79077587963</v>
+        <v>46111.624109212964</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.790777268514</v>
+        <v>46111.62411060186</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2912,13 +2912,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46064.975974479166</v>
+        <v>46064.809307812495</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.829439340276</v>
+        <v>46155.66277267361</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.82950846065</v>
+        <v>46155.66284179398</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2977,13 +2977,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46064.97597476852</v>
+        <v>46064.80930810185</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.651014675925</v>
+        <v>46112.48434800926</v>
       </c>
       <c r="D29" s="8">
-        <v>46112.651016296295</v>
+        <v>46112.48434962963</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3038,13 +3038,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46064.975975023146</v>
+        <v>46064.80930835648</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.55801283565</v>
+        <v>46154.39134616898</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.558014236114</v>
+        <v>46154.39134756944</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3099,13 +3099,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46064.97597528935</v>
+        <v>46064.80930862269</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.79065659722</v>
+        <v>46111.62398993055</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.79066731481</v>
+        <v>46111.62400064815</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3164,13 +3164,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46064.97597284723</v>
+        <v>46064.809306180556</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.79059375</v>
+        <v>46111.62392708333</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.790595659724</v>
+        <v>46111.62392899305</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3225,13 +3225,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46064.97597324074</v>
+        <v>46064.809306574076</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.79063767361</v>
+        <v>46111.62397100695</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.79063912037</v>
+        <v>46111.6239724537</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3286,13 +3286,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46064.975973506946</v>
+        <v>46064.80930684028</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.79054489583</v>
+        <v>46111.62387822916</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.79055864584</v>
+        <v>46111.623891979165</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3351,13 +3351,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46064.97597377315</v>
+        <v>46064.80930710648</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.790480682874</v>
+        <v>46111.6238140162</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.79048188658</v>
+        <v>46111.62381521991</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3412,13 +3412,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46064.975974050925</v>
+        <v>46064.80930738426</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.79051731482</v>
+        <v>46111.623850648146</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.79051883102</v>
+        <v>46111.62385216435</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3473,13 +3473,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46064.97597431713</v>
+        <v>46064.80930765046</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.79052896991</v>
+        <v>46111.62386230324</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.79053048611</v>
+        <v>46111.62386381945</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3534,13 +3534,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46064.97597459491</v>
+        <v>46064.80930792824</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.79043043981</v>
+        <v>46111.62376377315</v>
       </c>
       <c r="D38" s="5">
-        <v>46139.78184163195</v>
+        <v>46139.61517496528</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3599,13 +3599,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46064.97597487269</v>
+        <v>46064.80930820602</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.79036834491</v>
+        <v>46111.62370167824</v>
       </c>
       <c r="D39" s="8">
-        <v>46111.79036971065</v>
+        <v>46111.62370304398</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3660,13 +3660,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46064.97597515046</v>
+        <v>46064.8093084838</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.790416261574</v>
+        <v>46111.6237495949</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.79041780093</v>
+        <v>46111.62375113426</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3721,13 +3721,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46064.97597454861</v>
+        <v>46064.809307881944</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.768620312505</v>
+        <v>46114.60195364583</v>
       </c>
       <c r="D41" s="8">
-        <v>46139.781639733796</v>
+        <v>46139.61497306713</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3770,13 +3770,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.66955917824</v>
+        <v>46070.50289251158</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.513817430554</v>
+        <v>46114.34715076389</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.51383626157</v>
+        <v>46114.34716959491</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3835,13 +3835,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46064.97597483796</v>
+        <v>46064.8093081713</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.51387333333</v>
+        <v>46114.347206666665</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.513888587964</v>
+        <v>46114.3472219213</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3900,13 +3900,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46087.50355304398</v>
+        <v>46087.336886377314</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.513921412035</v>
+        <v>46114.34725474537</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.51393545139</v>
+        <v>46114.347268784724</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3965,13 +3965,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46087.50359630787</v>
+        <v>46087.3369296412</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.768603275465</v>
+        <v>46114.6019366088</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.181483541666</v>
+        <v>46127.014816875</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4028,13 +4028,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46064.97597513889</v>
+        <v>46064.80930847222</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.71552679398</v>
+        <v>46107.54886012731</v>
       </c>
       <c r="D46" s="5">
-        <v>46139.7815396875</v>
+        <v>46139.61487302084</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4077,13 +4077,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46064.97597543981</v>
+        <v>46064.80930877315</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.71551097222</v>
+        <v>46107.54884430555</v>
       </c>
       <c r="D47" s="8">
-        <v>46139.78147785879</v>
+        <v>46139.61481119213</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4142,13 +4142,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46064.97597572916</v>
+        <v>46064.809309062504</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.71543211806</v>
+        <v>46107.548765451385</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.78149715278</v>
+        <v>46139.61483048611</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4207,13 +4207,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46064.975976030095</v>
+        <v>46064.80930936342</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.71566543981</v>
+        <v>46107.54899877315</v>
       </c>
       <c r="D49" s="8">
-        <v>46139.781448344904</v>
+        <v>46139.61478167824</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4256,13 +4256,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46064.975976319445</v>
+        <v>46064.809309652774</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.71520322916</v>
+        <v>46107.5485365625</v>
       </c>
       <c r="D50" s="5">
-        <v>46139.78134862268</v>
+        <v>46139.61468195602</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4321,13 +4321,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46064.97597666667</v>
+        <v>46064.80931</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.71531623843</v>
+        <v>46107.54864957176</v>
       </c>
       <c r="D51" s="8">
-        <v>46139.7813684838</v>
+        <v>46139.61470181713</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4386,13 +4386,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46064.9759734838</v>
+        <v>46064.80930681713</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.71564938658</v>
+        <v>46107.548982719905</v>
       </c>
       <c r="D52" s="5">
-        <v>46139.781402106484</v>
+        <v>46139.61473543981</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4449,13 +4449,13 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46064.975973865745</v>
+        <v>46064.80930719907</v>
       </c>
       <c r="C53" s="8">
-        <v>46155.82935329861</v>
+        <v>46155.66268663194</v>
       </c>
       <c r="D53" s="8">
-        <v>46155.82935478009</v>
+        <v>46155.66268811343</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4498,13 +4498,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46064.97597451389</v>
+        <v>46064.80930784722</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.71485509259</v>
+        <v>46107.54818842592</v>
       </c>
       <c r="D54" s="5">
-        <v>46139.7811046412</v>
+        <v>46139.61443797454</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4561,13 +4561,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46064.97597511574</v>
+        <v>46064.809308449076</v>
       </c>
       <c r="C55" s="8">
-        <v>46154.558066516205</v>
+        <v>46154.39139984954</v>
       </c>
       <c r="D55" s="8">
-        <v>46155.82954369213</v>
+        <v>46155.66287702546</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>56</v>
@@ -4624,13 +4624,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46064.97597422454</v>
+        <v>46064.809307557865</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.71470586806</v>
+        <v>46107.548039201385</v>
       </c>
       <c r="D56" s="5">
-        <v>46139.78107806713</v>
+        <v>46139.614411400464</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4687,13 +4687,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.50497587963</v>
+        <v>46065.338309212966</v>
       </c>
       <c r="C57" s="8">
-        <v>46107.714572083336</v>
+        <v>46107.547905416664</v>
       </c>
       <c r="D57" s="8">
-        <v>46139.78105626158</v>
+        <v>46139.614389594906</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4750,13 +4750,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46064.97597565972</v>
+        <v>46064.809308993055</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.71504505787</v>
+        <v>46107.548378391206</v>
       </c>
       <c r="D58" s="5">
-        <v>46139.78125670139</v>
+        <v>46139.61459003472</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4799,13 +4799,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46064.975975925925</v>
+        <v>46064.80930925926</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.71502270833</v>
+        <v>46107.54835604166</v>
       </c>
       <c r="D59" s="8">
-        <v>46120.17345672454</v>
+        <v>46120.00679005787</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4864,13 +4864,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46064.97597623843</v>
+        <v>46064.80930957176</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.7136993287</v>
+        <v>46107.54703266204</v>
       </c>
       <c r="D60" s="5">
-        <v>46139.781139259256</v>
+        <v>46139.61447259259</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -4927,13 +4927,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46064.9759734375</v>
+        <v>46064.80930677083</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.713914548614</v>
+        <v>46107.54724788194</v>
       </c>
       <c r="D61" s="8">
-        <v>46139.78116083333</v>
+        <v>46139.61449416667</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>222</v>
@@ -4990,13 +4990,13 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46064.97597377315</v>
+        <v>46064.80930710648</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.71404958333</v>
+        <v>46107.547382916666</v>
       </c>
       <c r="D62" s="5">
-        <v>46139.78118356482</v>
+        <v>46139.614516898146</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5053,13 +5053,13 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46064.97597429398</v>
+        <v>46064.809307627314</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.71416802083</v>
+        <v>46107.547501354165</v>
       </c>
       <c r="D63" s="8">
-        <v>46126.207354363425</v>
+        <v>46126.04068769676</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5116,13 +5116,13 @@
         <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46064.97597454861</v>
+        <v>46064.809307881944</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.71432141204</v>
+        <v>46107.54765474537</v>
       </c>
       <c r="D64" s="5">
-        <v>46139.78120690973</v>
+        <v>46139.614540243056</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5179,11 +5179,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46064.97597479167</v>
+        <v>46064.809308125</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.71022986111</v>
+        <v>46197.54356319444</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5226,13 +5226,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46064.9759750463</v>
+        <v>46064.80930837963</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.5838743287</v>
+        <v>46197.41720766204</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.583876261575</v>
+        <v>46197.4172095949</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5289,13 +5289,13 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46064.97597528935</v>
+        <v>46064.80930862269</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.71009467593</v>
+        <v>46197.54342800926</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.71009662037</v>
+        <v>46197.5434299537</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5352,13 +5352,13 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46064.975975532405</v>
+        <v>46064.80930886574</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.71018288194</v>
+        <v>46197.54351621528</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.71018483797</v>
+        <v>46197.5435181713</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5415,13 +5415,13 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46064.975975787034</v>
+        <v>46064.80930912037</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.71022226852</v>
+        <v>46197.54355560185</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.71049135417</v>
+        <v>46197.5438246875</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>251</v>
@@ -5478,11 +5478,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46064.97597357639</v>
+        <v>46064.80930690972</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.792140254634</v>
+        <v>46126.62547358796</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>254</v>
@@ -5525,11 +5525,11 @@
         <v>256</v>
       </c>
       <c r="B71" s="8">
-        <v>46064.97597436343</v>
+        <v>46064.80930769676</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.71023167824</v>
+        <v>46197.54356501157</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>257</v>
@@ -5588,11 +5588,11 @@
         <v>260</v>
       </c>
       <c r="B72" s="5">
-        <v>46064.975974050925</v>
+        <v>46064.80930738426</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.710233125</v>
+        <v>46197.543566458335</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>261</v>
@@ -5651,11 +5651,11 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.53176077546</v>
+        <v>46090.3650941088</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46126.792140405094</v>
+        <v>46126.62547373843</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5698,11 +5698,11 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.53365568287</v>
+        <v>46090.366989016205</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46197.71023440972</v>
+        <v>46197.54356774305</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5761,11 +5761,11 @@
         <v>269</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.53385733796</v>
+        <v>46090.3671906713</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46161.167864664356</v>
+        <v>46161.001197997684</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>270</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -1450,13 +1450,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46064.809313460646</v>
+        <v>46064.97598012732</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.573083449075</v>
+        <v>46092.73975011574</v>
       </c>
       <c r="D4" s="5">
-        <v>46127.420010173606</v>
+        <v>46127.58667684028</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1499,13 +1499,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46064.80931388889</v>
+        <v>46064.97598055555</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.57305327547</v>
+        <v>46092.739719942125</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.57308410879</v>
+        <v>46092.739750775465</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1564,13 +1564,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46064.809314212966</v>
+        <v>46064.97598087963</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.57305391204</v>
+        <v>46092.7397205787</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.57308402778</v>
+        <v>46092.73975069444</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1629,13 +1629,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46064.80931452547</v>
+        <v>46064.975981192125</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.57305435185</v>
+        <v>46092.739721018515</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.5730846875</v>
+        <v>46092.739751354165</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1694,13 +1694,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46064.80931484954</v>
+        <v>46064.9759815162</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.57305482639</v>
+        <v>46092.73972149305</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.62625699074</v>
+        <v>46100.79292365741</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1759,13 +1759,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46064.80931515046</v>
+        <v>46064.97598181713</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.57305549768</v>
+        <v>46092.73972216435</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.573090370366</v>
+        <v>46092.73975703704</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1824,11 +1824,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46064.80931546296</v>
+        <v>46064.97598212963</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46196.61809625</v>
+        <v>46196.784762916664</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1871,13 +1871,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46064.80931575231</v>
+        <v>46064.97598241898</v>
       </c>
       <c r="C11" s="8">
-        <v>46112.484149675925</v>
+        <v>46112.65081634259</v>
       </c>
       <c r="D11" s="8">
-        <v>46112.48417648148</v>
+        <v>46112.65084314815</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1936,13 +1936,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46064.80931606481</v>
+        <v>46064.975982731485</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.61808811342</v>
+        <v>46196.78475478009</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.61809138889</v>
+        <v>46196.78475805555</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2001,13 +2001,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46064.80931635416</v>
+        <v>46064.975983020835</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.347010219906</v>
+        <v>46114.51367688658</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.34702380787</v>
+        <v>46114.51369047454</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2054,13 +2054,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46064.809306967596</v>
+        <v>46064.97597363426</v>
       </c>
       <c r="C14" s="5">
-        <v>46111.623314745375</v>
+        <v>46111.78998141203</v>
       </c>
       <c r="D14" s="5">
-        <v>46111.62331697917</v>
+        <v>46111.78998364584</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2119,13 +2119,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46064.80930760417</v>
+        <v>46064.975974270834</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.62332436343</v>
+        <v>46111.78999103009</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.6233259375</v>
+        <v>46111.78999260417</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2184,13 +2184,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46064.80930789352</v>
+        <v>46064.975974560184</v>
       </c>
       <c r="C16" s="5">
-        <v>46111.62333570602</v>
+        <v>46111.79000237268</v>
       </c>
       <c r="D16" s="5">
-        <v>46111.623337349534</v>
+        <v>46111.790004016206</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2249,13 +2249,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46064.80930815972</v>
+        <v>46064.97597482639</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34699280093</v>
+        <v>46114.51365946759</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.3470103125</v>
+        <v>46114.51367697917</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2314,13 +2314,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46064.8093084375</v>
+        <v>46064.97597510417</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.48433127315</v>
+        <v>46112.65099793981</v>
       </c>
       <c r="D18" s="5">
-        <v>46139.61509335648</v>
+        <v>46139.78176002315</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2363,13 +2363,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46064.80930898148</v>
+        <v>46064.97597564815</v>
       </c>
       <c r="C19" s="8">
-        <v>46111.623400972225</v>
+        <v>46111.79006763889</v>
       </c>
       <c r="D19" s="8">
-        <v>46111.62341542824</v>
+        <v>46111.79008209491</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2428,13 +2428,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46064.809308703705</v>
+        <v>46064.97597537037</v>
       </c>
       <c r="C20" s="5">
-        <v>46111.62341221065</v>
+        <v>46111.79007887731</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.623428101855</v>
+        <v>46111.79009476852</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -2493,13 +2493,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46064.80930923611</v>
+        <v>46064.97597590278</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.48430203703</v>
+        <v>46112.6509687037</v>
       </c>
       <c r="D21" s="8">
-        <v>46112.48433341435</v>
+        <v>46112.65100008102</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2558,13 +2558,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46064.809309502314</v>
+        <v>46064.97597616898</v>
       </c>
       <c r="C22" s="5">
-        <v>46111.62344167824</v>
+        <v>46111.79010834491</v>
       </c>
       <c r="D22" s="5">
-        <v>46111.62345855324</v>
+        <v>46111.79012521991</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2623,13 +2623,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46064.80930645834</v>
+        <v>46064.975973125</v>
       </c>
       <c r="C23" s="8">
-        <v>46111.62349084491</v>
+        <v>46111.790157511576</v>
       </c>
       <c r="D23" s="8">
-        <v>46111.62350752315</v>
+        <v>46111.79017418981</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2688,13 +2688,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46064.80930671297</v>
+        <v>46064.97597337963</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.597614976854</v>
+        <v>46114.76428164352</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.662779502316</v>
+        <v>46155.82944616898</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2737,13 +2737,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46064.809306967596</v>
+        <v>46064.97597363426</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.62412446759</v>
+        <v>46111.79079113426</v>
       </c>
       <c r="D25" s="8">
-        <v>46139.61514642361</v>
+        <v>46139.781813090274</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2802,13 +2802,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46064.820425868056</v>
+        <v>46064.98709253472</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.624070405094</v>
+        <v>46111.79073707176</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.62407200232</v>
+        <v>46111.79073866898</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2857,13 +2857,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46064.82027923611</v>
+        <v>46064.98694590278</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.624109212964</v>
+        <v>46111.79077587963</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.62411060186</v>
+        <v>46111.790777268514</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2912,13 +2912,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46064.809307812495</v>
+        <v>46064.975974479166</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.66277267361</v>
+        <v>46155.829439340276</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.66284179398</v>
+        <v>46155.82950846065</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2977,13 +2977,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46064.80930810185</v>
+        <v>46064.97597476852</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.48434800926</v>
+        <v>46112.651014675925</v>
       </c>
       <c r="D29" s="8">
-        <v>46112.48434962963</v>
+        <v>46112.651016296295</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3038,13 +3038,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46064.80930835648</v>
+        <v>46064.975975023146</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.39134616898</v>
+        <v>46154.55801283565</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.39134756944</v>
+        <v>46154.558014236114</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3099,13 +3099,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46064.80930862269</v>
+        <v>46064.97597528935</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.62398993055</v>
+        <v>46111.79065659722</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.62400064815</v>
+        <v>46111.79066731481</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3164,13 +3164,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46064.809306180556</v>
+        <v>46064.97597284723</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.62392708333</v>
+        <v>46111.79059375</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.62392899305</v>
+        <v>46111.790595659724</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3225,13 +3225,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46064.809306574076</v>
+        <v>46064.97597324074</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.62397100695</v>
+        <v>46111.79063767361</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.6239724537</v>
+        <v>46111.79063912037</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3286,13 +3286,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46064.80930684028</v>
+        <v>46064.975973506946</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.62387822916</v>
+        <v>46111.79054489583</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.623891979165</v>
+        <v>46111.79055864584</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3351,13 +3351,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46064.80930710648</v>
+        <v>46064.97597377315</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.6238140162</v>
+        <v>46111.790480682874</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.62381521991</v>
+        <v>46111.79048188658</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3412,13 +3412,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46064.80930738426</v>
+        <v>46064.975974050925</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.623850648146</v>
+        <v>46111.79051731482</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.62385216435</v>
+        <v>46111.79051883102</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3473,13 +3473,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46064.80930765046</v>
+        <v>46064.97597431713</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.62386230324</v>
+        <v>46111.79052896991</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.62386381945</v>
+        <v>46111.79053048611</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3534,13 +3534,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46064.80930792824</v>
+        <v>46064.97597459491</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.62376377315</v>
+        <v>46111.79043043981</v>
       </c>
       <c r="D38" s="5">
-        <v>46139.61517496528</v>
+        <v>46139.78184163195</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3599,13 +3599,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46064.80930820602</v>
+        <v>46064.97597487269</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.62370167824</v>
+        <v>46111.79036834491</v>
       </c>
       <c r="D39" s="8">
-        <v>46111.62370304398</v>
+        <v>46111.79036971065</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3660,13 +3660,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46064.8093084838</v>
+        <v>46064.97597515046</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.6237495949</v>
+        <v>46111.790416261574</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.62375113426</v>
+        <v>46111.79041780093</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3721,13 +3721,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46064.809307881944</v>
+        <v>46064.97597454861</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.60195364583</v>
+        <v>46114.768620312505</v>
       </c>
       <c r="D41" s="8">
-        <v>46139.61497306713</v>
+        <v>46139.781639733796</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3770,13 +3770,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.50289251158</v>
+        <v>46070.66955917824</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.34715076389</v>
+        <v>46114.513817430554</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.34716959491</v>
+        <v>46114.51383626157</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3835,13 +3835,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46064.8093081713</v>
+        <v>46064.97597483796</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.347206666665</v>
+        <v>46114.51387333333</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.3472219213</v>
+        <v>46114.513888587964</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3900,13 +3900,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46087.336886377314</v>
+        <v>46087.50355304398</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.34725474537</v>
+        <v>46114.513921412035</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.347268784724</v>
+        <v>46114.51393545139</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3965,13 +3965,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46087.3369296412</v>
+        <v>46087.50359630787</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.6019366088</v>
+        <v>46114.768603275465</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.014816875</v>
+        <v>46127.181483541666</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4028,13 +4028,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46064.80930847222</v>
+        <v>46064.97597513889</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.54886012731</v>
+        <v>46107.71552679398</v>
       </c>
       <c r="D46" s="5">
-        <v>46139.61487302084</v>
+        <v>46139.7815396875</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4077,13 +4077,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46064.80930877315</v>
+        <v>46064.97597543981</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.54884430555</v>
+        <v>46107.71551097222</v>
       </c>
       <c r="D47" s="8">
-        <v>46139.61481119213</v>
+        <v>46139.78147785879</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4142,13 +4142,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46064.809309062504</v>
+        <v>46064.97597572916</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.548765451385</v>
+        <v>46107.71543211806</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.61483048611</v>
+        <v>46139.78149715278</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4207,13 +4207,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46064.80930936342</v>
+        <v>46064.975976030095</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.54899877315</v>
+        <v>46107.71566543981</v>
       </c>
       <c r="D49" s="8">
-        <v>46139.61478167824</v>
+        <v>46139.781448344904</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4256,13 +4256,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46064.809309652774</v>
+        <v>46064.975976319445</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.5485365625</v>
+        <v>46107.71520322916</v>
       </c>
       <c r="D50" s="5">
-        <v>46139.61468195602</v>
+        <v>46139.78134862268</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4321,13 +4321,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46064.80931</v>
+        <v>46064.97597666667</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.54864957176</v>
+        <v>46107.71531623843</v>
       </c>
       <c r="D51" s="8">
-        <v>46139.61470181713</v>
+        <v>46139.7813684838</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4386,13 +4386,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46064.80930681713</v>
+        <v>46064.9759734838</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.548982719905</v>
+        <v>46107.71564938658</v>
       </c>
       <c r="D52" s="5">
-        <v>46139.61473543981</v>
+        <v>46139.781402106484</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4449,13 +4449,13 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46064.80930719907</v>
+        <v>46064.975973865745</v>
       </c>
       <c r="C53" s="8">
-        <v>46155.66268663194</v>
+        <v>46155.82935329861</v>
       </c>
       <c r="D53" s="8">
-        <v>46155.66268811343</v>
+        <v>46155.82935478009</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4498,13 +4498,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46064.80930784722</v>
+        <v>46064.97597451389</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.54818842592</v>
+        <v>46107.71485509259</v>
       </c>
       <c r="D54" s="5">
-        <v>46139.61443797454</v>
+        <v>46139.7811046412</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4561,13 +4561,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46064.809308449076</v>
+        <v>46064.97597511574</v>
       </c>
       <c r="C55" s="8">
-        <v>46154.39139984954</v>
+        <v>46154.558066516205</v>
       </c>
       <c r="D55" s="8">
-        <v>46155.66287702546</v>
+        <v>46155.82954369213</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>56</v>
@@ -4624,13 +4624,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46064.809307557865</v>
+        <v>46064.97597422454</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.548039201385</v>
+        <v>46107.71470586806</v>
       </c>
       <c r="D56" s="5">
-        <v>46139.614411400464</v>
+        <v>46139.78107806713</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4687,13 +4687,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.338309212966</v>
+        <v>46065.50497587963</v>
       </c>
       <c r="C57" s="8">
-        <v>46107.547905416664</v>
+        <v>46107.714572083336</v>
       </c>
       <c r="D57" s="8">
-        <v>46139.614389594906</v>
+        <v>46139.78105626158</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4750,13 +4750,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46064.809308993055</v>
+        <v>46064.97597565972</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.548378391206</v>
+        <v>46107.71504505787</v>
       </c>
       <c r="D58" s="5">
-        <v>46139.61459003472</v>
+        <v>46139.78125670139</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4799,13 +4799,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46064.80930925926</v>
+        <v>46064.975975925925</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.54835604166</v>
+        <v>46107.71502270833</v>
       </c>
       <c r="D59" s="8">
-        <v>46120.00679005787</v>
+        <v>46120.17345672454</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4864,13 +4864,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46064.80930957176</v>
+        <v>46064.97597623843</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.54703266204</v>
+        <v>46107.7136993287</v>
       </c>
       <c r="D60" s="5">
-        <v>46139.61447259259</v>
+        <v>46139.781139259256</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -4927,13 +4927,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46064.80930677083</v>
+        <v>46064.9759734375</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.54724788194</v>
+        <v>46107.713914548614</v>
       </c>
       <c r="D61" s="8">
-        <v>46139.61449416667</v>
+        <v>46139.78116083333</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>222</v>
@@ -4990,13 +4990,13 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46064.80930710648</v>
+        <v>46064.97597377315</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.547382916666</v>
+        <v>46107.71404958333</v>
       </c>
       <c r="D62" s="5">
-        <v>46139.614516898146</v>
+        <v>46139.78118356482</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5053,13 +5053,13 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46064.809307627314</v>
+        <v>46064.97597429398</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.547501354165</v>
+        <v>46107.71416802083</v>
       </c>
       <c r="D63" s="8">
-        <v>46126.04068769676</v>
+        <v>46126.207354363425</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5116,13 +5116,13 @@
         <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46064.809307881944</v>
+        <v>46064.97597454861</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.54765474537</v>
+        <v>46107.71432141204</v>
       </c>
       <c r="D64" s="5">
-        <v>46139.614540243056</v>
+        <v>46139.78120690973</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5179,11 +5179,11 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46064.809308125</v>
+        <v>46064.97597479167</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46197.54356319444</v>
+        <v>46197.71022986111</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5226,13 +5226,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46064.80930837963</v>
+        <v>46064.9759750463</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.41720766204</v>
+        <v>46197.5838743287</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.4172095949</v>
+        <v>46197.583876261575</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5289,13 +5289,13 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46064.80930862269</v>
+        <v>46064.97597528935</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.54342800926</v>
+        <v>46197.71009467593</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.5434299537</v>
+        <v>46197.71009662037</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5352,13 +5352,13 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46064.80930886574</v>
+        <v>46064.975975532405</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.54351621528</v>
+        <v>46197.71018288194</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.5435181713</v>
+        <v>46197.71018483797</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5415,13 +5415,13 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46064.80930912037</v>
+        <v>46064.975975787034</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.54355560185</v>
+        <v>46197.71022226852</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.5438246875</v>
+        <v>46197.71049135417</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>251</v>
@@ -5478,11 +5478,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46064.80930690972</v>
+        <v>46064.97597357639</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.62547358796</v>
+        <v>46126.792140254634</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>254</v>
@@ -5525,11 +5525,11 @@
         <v>256</v>
       </c>
       <c r="B71" s="8">
-        <v>46064.80930769676</v>
+        <v>46064.97597436343</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.54356501157</v>
+        <v>46197.71023167824</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>257</v>
@@ -5588,11 +5588,11 @@
         <v>260</v>
       </c>
       <c r="B72" s="5">
-        <v>46064.80930738426</v>
+        <v>46064.975974050925</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.543566458335</v>
+        <v>46197.710233125</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>261</v>
@@ -5651,11 +5651,11 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.3650941088</v>
+        <v>46090.53176077546</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46126.62547373843</v>
+        <v>46126.792140405094</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5698,11 +5698,11 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.366989016205</v>
+        <v>46090.53365568287</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46197.54356774305</v>
+        <v>46197.71023440972</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5761,11 +5761,11 @@
         <v>269</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.3671906713</v>
+        <v>46090.53385733796</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46161.001197997684</v>
+        <v>46161.167864664356</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>270</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -1826,9 +1826,11 @@
       <c r="B10" s="5">
         <v>46064.97598212963</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46198.63353439815</v>
+      </c>
       <c r="D10" s="5">
-        <v>46196.784762916664</v>
+        <v>46198.633536724534</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -5181,9 +5183,11 @@
       <c r="B65" s="8">
         <v>46064.97597479167</v>
       </c>
-      <c r="C65" s="9"/>
+      <c r="C65" s="8">
+        <v>46198.63385663195</v>
+      </c>
       <c r="D65" s="8">
-        <v>46197.71022986111</v>
+        <v>46198.63385799769</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5232,7 +5236,7 @@
         <v>46197.5838743287</v>
       </c>
       <c r="D66" s="5">
-        <v>46197.583876261575</v>
+        <v>46198.63395618055</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5275,7 +5279,7 @@
         <v>46135</v>
       </c>
       <c r="S66" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="10" t="s">
         <v>31</v>
@@ -5295,7 +5299,7 @@
         <v>46197.71009467593</v>
       </c>
       <c r="D67" s="8">
-        <v>46197.71009662037</v>
+        <v>46198.63395686343</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5338,7 +5342,7 @@
         <v>46136</v>
       </c>
       <c r="S67" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="10" t="s">
         <v>31</v>
@@ -5358,7 +5362,7 @@
         <v>46197.71018288194</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.71018483797</v>
+        <v>46198.633957453705</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5401,7 +5405,7 @@
         <v>46139</v>
       </c>
       <c r="S68" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" s="12" t="s">
         <v>249</v>
@@ -5421,7 +5425,7 @@
         <v>46197.71022226852</v>
       </c>
       <c r="D69" s="8">
-        <v>46197.71049135417</v>
+        <v>46198.63395809028</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>251</v>
@@ -5464,7 +5468,7 @@
         <v>46140</v>
       </c>
       <c r="S69" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
         <v>249</v>
@@ -5653,9 +5657,11 @@
       <c r="B73" s="8">
         <v>46090.53176077546</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46198.63384538195</v>
+      </c>
       <c r="D73" s="8">
-        <v>46126.792140405094</v>
+        <v>46198.63384679398</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5700,9 +5706,11 @@
       <c r="B74" s="5">
         <v>46090.53365568287</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46198.63364987269</v>
+      </c>
       <c r="D74" s="5">
-        <v>46197.71023440972</v>
+        <v>46198.633871805556</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5747,7 +5755,7 @@
         <v>46141</v>
       </c>
       <c r="S74" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="11" t="s">
         <v>115</v>
@@ -5763,9 +5771,11 @@
       <c r="B75" s="8">
         <v>46090.53385733796</v>
       </c>
-      <c r="C75" s="9"/>
+      <c r="C75" s="8">
+        <v>46198.63376841435</v>
+      </c>
       <c r="D75" s="8">
-        <v>46161.167864664356</v>
+        <v>46198.63389696759</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>270</v>
@@ -5810,7 +5820,7 @@
         <v>46153</v>
       </c>
       <c r="S75" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" s="11" t="s">
         <v>115</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -1450,13 +1450,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46064.97598012732</v>
+        <v>46064.809313460646</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.73975011574</v>
+        <v>46092.573083449075</v>
       </c>
       <c r="D4" s="5">
-        <v>46127.58667684028</v>
+        <v>46127.420010173606</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1499,13 +1499,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46064.97598055555</v>
+        <v>46064.80931388889</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.739719942125</v>
+        <v>46092.57305327547</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.739750775465</v>
+        <v>46092.57308410879</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1564,13 +1564,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46064.97598087963</v>
+        <v>46064.809314212966</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.7397205787</v>
+        <v>46092.57305391204</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.73975069444</v>
+        <v>46092.57308402778</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1629,13 +1629,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46064.975981192125</v>
+        <v>46064.80931452547</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.739721018515</v>
+        <v>46092.57305435185</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.739751354165</v>
+        <v>46092.5730846875</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1694,13 +1694,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46064.9759815162</v>
+        <v>46064.80931484954</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.73972149305</v>
+        <v>46092.57305482639</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.79292365741</v>
+        <v>46100.62625699074</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1759,13 +1759,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46064.97598181713</v>
+        <v>46064.80931515046</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.73972216435</v>
+        <v>46092.57305549768</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.73975703704</v>
+        <v>46092.573090370366</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1824,13 +1824,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46064.97598212963</v>
+        <v>46064.80931546296</v>
       </c>
       <c r="C10" s="5">
-        <v>46198.63353439815</v>
+        <v>46198.46686773148</v>
       </c>
       <c r="D10" s="5">
-        <v>46198.633536724534</v>
+        <v>46198.46687005787</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1873,13 +1873,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46064.97598241898</v>
+        <v>46064.80931575231</v>
       </c>
       <c r="C11" s="8">
-        <v>46112.65081634259</v>
+        <v>46112.484149675925</v>
       </c>
       <c r="D11" s="8">
-        <v>46112.65084314815</v>
+        <v>46112.48417648148</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1938,13 +1938,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46064.975982731485</v>
+        <v>46064.80931606481</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.78475478009</v>
+        <v>46196.61808811342</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.78475805555</v>
+        <v>46196.61809138889</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2003,13 +2003,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46064.975983020835</v>
+        <v>46064.80931635416</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.51367688658</v>
+        <v>46114.347010219906</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.51369047454</v>
+        <v>46114.34702380787</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2056,13 +2056,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46064.97597363426</v>
+        <v>46064.809306967596</v>
       </c>
       <c r="C14" s="5">
-        <v>46111.78998141203</v>
+        <v>46111.623314745375</v>
       </c>
       <c r="D14" s="5">
-        <v>46111.78998364584</v>
+        <v>46111.62331697917</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2121,13 +2121,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46064.975974270834</v>
+        <v>46064.80930760417</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.78999103009</v>
+        <v>46111.62332436343</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.78999260417</v>
+        <v>46111.6233259375</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2186,13 +2186,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46064.975974560184</v>
+        <v>46064.80930789352</v>
       </c>
       <c r="C16" s="5">
-        <v>46111.79000237268</v>
+        <v>46111.62333570602</v>
       </c>
       <c r="D16" s="5">
-        <v>46111.790004016206</v>
+        <v>46111.623337349534</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2251,13 +2251,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46064.97597482639</v>
+        <v>46064.80930815972</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.51365946759</v>
+        <v>46114.34699280093</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.51367697917</v>
+        <v>46114.3470103125</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2316,13 +2316,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46064.97597510417</v>
+        <v>46064.8093084375</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.65099793981</v>
+        <v>46112.48433127315</v>
       </c>
       <c r="D18" s="5">
-        <v>46139.78176002315</v>
+        <v>46139.61509335648</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2365,13 +2365,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46064.97597564815</v>
+        <v>46064.80930898148</v>
       </c>
       <c r="C19" s="8">
-        <v>46111.79006763889</v>
+        <v>46111.623400972225</v>
       </c>
       <c r="D19" s="8">
-        <v>46111.79008209491</v>
+        <v>46111.62341542824</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2430,13 +2430,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46064.97597537037</v>
+        <v>46064.809308703705</v>
       </c>
       <c r="C20" s="5">
-        <v>46111.79007887731</v>
+        <v>46111.62341221065</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.79009476852</v>
+        <v>46111.623428101855</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -2495,13 +2495,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46064.97597590278</v>
+        <v>46064.80930923611</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.6509687037</v>
+        <v>46112.48430203703</v>
       </c>
       <c r="D21" s="8">
-        <v>46112.65100008102</v>
+        <v>46112.48433341435</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2560,13 +2560,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46064.97597616898</v>
+        <v>46064.809309502314</v>
       </c>
       <c r="C22" s="5">
-        <v>46111.79010834491</v>
+        <v>46111.62344167824</v>
       </c>
       <c r="D22" s="5">
-        <v>46111.79012521991</v>
+        <v>46111.62345855324</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2625,13 +2625,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46064.975973125</v>
+        <v>46064.80930645834</v>
       </c>
       <c r="C23" s="8">
-        <v>46111.790157511576</v>
+        <v>46111.62349084491</v>
       </c>
       <c r="D23" s="8">
-        <v>46111.79017418981</v>
+        <v>46111.62350752315</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2690,13 +2690,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46064.97597337963</v>
+        <v>46064.80930671297</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.76428164352</v>
+        <v>46114.597614976854</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.82944616898</v>
+        <v>46155.662779502316</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2739,13 +2739,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46064.97597363426</v>
+        <v>46064.809306967596</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.79079113426</v>
+        <v>46111.62412446759</v>
       </c>
       <c r="D25" s="8">
-        <v>46139.781813090274</v>
+        <v>46139.61514642361</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2804,13 +2804,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46064.98709253472</v>
+        <v>46064.820425868056</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.79073707176</v>
+        <v>46111.624070405094</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.79073866898</v>
+        <v>46111.62407200232</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2859,13 +2859,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46064.98694590278</v>
+        <v>46064.82027923611</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.79077587963</v>
+        <v>46111.624109212964</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.790777268514</v>
+        <v>46111.62411060186</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2914,13 +2914,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46064.975974479166</v>
+        <v>46064.809307812495</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.829439340276</v>
+        <v>46155.66277267361</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.82950846065</v>
+        <v>46155.66284179398</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2979,13 +2979,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46064.97597476852</v>
+        <v>46064.80930810185</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.651014675925</v>
+        <v>46112.48434800926</v>
       </c>
       <c r="D29" s="8">
-        <v>46112.651016296295</v>
+        <v>46112.48434962963</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3040,13 +3040,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46064.975975023146</v>
+        <v>46064.80930835648</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.55801283565</v>
+        <v>46154.39134616898</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.558014236114</v>
+        <v>46154.39134756944</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3101,13 +3101,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46064.97597528935</v>
+        <v>46064.80930862269</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.79065659722</v>
+        <v>46111.62398993055</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.79066731481</v>
+        <v>46111.62400064815</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3166,13 +3166,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46064.97597284723</v>
+        <v>46064.809306180556</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.79059375</v>
+        <v>46111.62392708333</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.790595659724</v>
+        <v>46111.62392899305</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3227,13 +3227,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46064.97597324074</v>
+        <v>46064.809306574076</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.79063767361</v>
+        <v>46111.62397100695</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.79063912037</v>
+        <v>46111.6239724537</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3288,13 +3288,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46064.975973506946</v>
+        <v>46064.80930684028</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.79054489583</v>
+        <v>46111.62387822916</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.79055864584</v>
+        <v>46111.623891979165</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3353,13 +3353,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46064.97597377315</v>
+        <v>46064.80930710648</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.790480682874</v>
+        <v>46111.6238140162</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.79048188658</v>
+        <v>46111.62381521991</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3414,13 +3414,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46064.975974050925</v>
+        <v>46064.80930738426</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.79051731482</v>
+        <v>46111.623850648146</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.79051883102</v>
+        <v>46111.62385216435</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3475,13 +3475,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46064.97597431713</v>
+        <v>46064.80930765046</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.79052896991</v>
+        <v>46111.62386230324</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.79053048611</v>
+        <v>46111.62386381945</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3536,13 +3536,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46064.97597459491</v>
+        <v>46064.80930792824</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.79043043981</v>
+        <v>46111.62376377315</v>
       </c>
       <c r="D38" s="5">
-        <v>46139.78184163195</v>
+        <v>46139.61517496528</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3601,13 +3601,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46064.97597487269</v>
+        <v>46064.80930820602</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.79036834491</v>
+        <v>46111.62370167824</v>
       </c>
       <c r="D39" s="8">
-        <v>46111.79036971065</v>
+        <v>46111.62370304398</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3662,13 +3662,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46064.97597515046</v>
+        <v>46064.8093084838</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.790416261574</v>
+        <v>46111.6237495949</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.79041780093</v>
+        <v>46111.62375113426</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3723,13 +3723,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46064.97597454861</v>
+        <v>46064.809307881944</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.768620312505</v>
+        <v>46114.60195364583</v>
       </c>
       <c r="D41" s="8">
-        <v>46139.781639733796</v>
+        <v>46139.61497306713</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3772,13 +3772,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.66955917824</v>
+        <v>46070.50289251158</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.513817430554</v>
+        <v>46114.34715076389</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.51383626157</v>
+        <v>46114.34716959491</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3837,13 +3837,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46064.97597483796</v>
+        <v>46064.8093081713</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.51387333333</v>
+        <v>46114.347206666665</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.513888587964</v>
+        <v>46114.3472219213</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3902,13 +3902,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46087.50355304398</v>
+        <v>46087.336886377314</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.513921412035</v>
+        <v>46114.34725474537</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.51393545139</v>
+        <v>46114.347268784724</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3967,13 +3967,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46087.50359630787</v>
+        <v>46087.3369296412</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.768603275465</v>
+        <v>46114.6019366088</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.181483541666</v>
+        <v>46127.014816875</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4030,13 +4030,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46064.97597513889</v>
+        <v>46064.80930847222</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.71552679398</v>
+        <v>46107.54886012731</v>
       </c>
       <c r="D46" s="5">
-        <v>46139.7815396875</v>
+        <v>46139.61487302084</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4079,13 +4079,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46064.97597543981</v>
+        <v>46064.80930877315</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.71551097222</v>
+        <v>46107.54884430555</v>
       </c>
       <c r="D47" s="8">
-        <v>46139.78147785879</v>
+        <v>46139.61481119213</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4144,13 +4144,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46064.97597572916</v>
+        <v>46064.809309062504</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.71543211806</v>
+        <v>46107.548765451385</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.78149715278</v>
+        <v>46139.61483048611</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4209,13 +4209,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46064.975976030095</v>
+        <v>46064.80930936342</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.71566543981</v>
+        <v>46107.54899877315</v>
       </c>
       <c r="D49" s="8">
-        <v>46139.781448344904</v>
+        <v>46139.61478167824</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4258,13 +4258,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46064.975976319445</v>
+        <v>46064.809309652774</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.71520322916</v>
+        <v>46107.5485365625</v>
       </c>
       <c r="D50" s="5">
-        <v>46139.78134862268</v>
+        <v>46139.61468195602</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4323,13 +4323,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46064.97597666667</v>
+        <v>46064.80931</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.71531623843</v>
+        <v>46107.54864957176</v>
       </c>
       <c r="D51" s="8">
-        <v>46139.7813684838</v>
+        <v>46139.61470181713</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4388,13 +4388,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46064.9759734838</v>
+        <v>46064.80930681713</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.71564938658</v>
+        <v>46107.548982719905</v>
       </c>
       <c r="D52" s="5">
-        <v>46139.781402106484</v>
+        <v>46139.61473543981</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4451,13 +4451,13 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46064.975973865745</v>
+        <v>46064.80930719907</v>
       </c>
       <c r="C53" s="8">
-        <v>46155.82935329861</v>
+        <v>46155.66268663194</v>
       </c>
       <c r="D53" s="8">
-        <v>46155.82935478009</v>
+        <v>46155.66268811343</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4500,13 +4500,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46064.97597451389</v>
+        <v>46064.80930784722</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.71485509259</v>
+        <v>46107.54818842592</v>
       </c>
       <c r="D54" s="5">
-        <v>46139.7811046412</v>
+        <v>46139.61443797454</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4563,13 +4563,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46064.97597511574</v>
+        <v>46064.809308449076</v>
       </c>
       <c r="C55" s="8">
-        <v>46154.558066516205</v>
+        <v>46154.39139984954</v>
       </c>
       <c r="D55" s="8">
-        <v>46155.82954369213</v>
+        <v>46155.66287702546</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>56</v>
@@ -4626,13 +4626,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46064.97597422454</v>
+        <v>46064.809307557865</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.71470586806</v>
+        <v>46107.548039201385</v>
       </c>
       <c r="D56" s="5">
-        <v>46139.78107806713</v>
+        <v>46139.614411400464</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4689,13 +4689,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.50497587963</v>
+        <v>46065.338309212966</v>
       </c>
       <c r="C57" s="8">
-        <v>46107.714572083336</v>
+        <v>46107.547905416664</v>
       </c>
       <c r="D57" s="8">
-        <v>46139.78105626158</v>
+        <v>46139.614389594906</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4752,13 +4752,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46064.97597565972</v>
+        <v>46064.809308993055</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.71504505787</v>
+        <v>46107.548378391206</v>
       </c>
       <c r="D58" s="5">
-        <v>46139.78125670139</v>
+        <v>46139.61459003472</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4801,13 +4801,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46064.975975925925</v>
+        <v>46064.80930925926</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.71502270833</v>
+        <v>46107.54835604166</v>
       </c>
       <c r="D59" s="8">
-        <v>46120.17345672454</v>
+        <v>46120.00679005787</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4866,13 +4866,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46064.97597623843</v>
+        <v>46064.80930957176</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.7136993287</v>
+        <v>46107.54703266204</v>
       </c>
       <c r="D60" s="5">
-        <v>46139.781139259256</v>
+        <v>46139.61447259259</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -4929,13 +4929,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46064.9759734375</v>
+        <v>46064.80930677083</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.713914548614</v>
+        <v>46107.54724788194</v>
       </c>
       <c r="D61" s="8">
-        <v>46139.78116083333</v>
+        <v>46139.61449416667</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>222</v>
@@ -4992,13 +4992,13 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46064.97597377315</v>
+        <v>46064.80930710648</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.71404958333</v>
+        <v>46107.547382916666</v>
       </c>
       <c r="D62" s="5">
-        <v>46139.78118356482</v>
+        <v>46139.614516898146</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5055,13 +5055,13 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46064.97597429398</v>
+        <v>46064.809307627314</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.71416802083</v>
+        <v>46107.547501354165</v>
       </c>
       <c r="D63" s="8">
-        <v>46126.207354363425</v>
+        <v>46126.04068769676</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5118,13 +5118,13 @@
         <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46064.97597454861</v>
+        <v>46064.809307881944</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.71432141204</v>
+        <v>46107.54765474537</v>
       </c>
       <c r="D64" s="5">
-        <v>46139.78120690973</v>
+        <v>46139.614540243056</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5181,13 +5181,13 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46064.97597479167</v>
+        <v>46064.809308125</v>
       </c>
       <c r="C65" s="8">
-        <v>46198.63385663195</v>
+        <v>46198.467189965275</v>
       </c>
       <c r="D65" s="8">
-        <v>46198.63385799769</v>
+        <v>46198.467191331016</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5230,13 +5230,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46064.9759750463</v>
+        <v>46064.80930837963</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.5838743287</v>
+        <v>46197.41720766204</v>
       </c>
       <c r="D66" s="5">
-        <v>46198.63395618055</v>
+        <v>46198.467289513894</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5293,13 +5293,13 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46064.97597528935</v>
+        <v>46064.80930862269</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.71009467593</v>
+        <v>46197.54342800926</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.63395686343</v>
+        <v>46198.46729019676</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5356,13 +5356,13 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46064.975975532405</v>
+        <v>46064.80930886574</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.71018288194</v>
+        <v>46197.54351621528</v>
       </c>
       <c r="D68" s="5">
-        <v>46198.633957453705</v>
+        <v>46198.46729078704</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5419,13 +5419,13 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46064.975975787034</v>
+        <v>46064.80930912037</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.71022226852</v>
+        <v>46197.54355560185</v>
       </c>
       <c r="D69" s="8">
-        <v>46198.63395809028</v>
+        <v>46198.467291423614</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>251</v>
@@ -5482,11 +5482,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46064.97597357639</v>
+        <v>46064.80930690972</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.792140254634</v>
+        <v>46126.62547358796</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>254</v>
@@ -5529,11 +5529,11 @@
         <v>256</v>
       </c>
       <c r="B71" s="8">
-        <v>46064.97597436343</v>
+        <v>46064.80930769676</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.71023167824</v>
+        <v>46197.54356501157</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>257</v>
@@ -5592,11 +5592,11 @@
         <v>260</v>
       </c>
       <c r="B72" s="5">
-        <v>46064.975974050925</v>
+        <v>46064.80930738426</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.710233125</v>
+        <v>46197.543566458335</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>261</v>
@@ -5655,13 +5655,13 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.53176077546</v>
+        <v>46090.3650941088</v>
       </c>
       <c r="C73" s="8">
-        <v>46198.63384538195</v>
+        <v>46198.46717871528</v>
       </c>
       <c r="D73" s="8">
-        <v>46198.63384679398</v>
+        <v>46198.467180127314</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5704,13 +5704,13 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.53365568287</v>
+        <v>46090.366989016205</v>
       </c>
       <c r="C74" s="5">
-        <v>46198.63364987269</v>
+        <v>46198.46698320602</v>
       </c>
       <c r="D74" s="5">
-        <v>46198.633871805556</v>
+        <v>46198.46720513889</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5769,13 +5769,13 @@
         <v>269</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.53385733796</v>
+        <v>46090.3671906713</v>
       </c>
       <c r="C75" s="8">
-        <v>46198.63376841435</v>
+        <v>46198.46710174769</v>
       </c>
       <c r="D75" s="8">
-        <v>46198.63389696759</v>
+        <v>46198.46723030093</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>270</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -1450,13 +1450,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46064.809313460646</v>
+        <v>46064.97598012732</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.573083449075</v>
+        <v>46092.73975011574</v>
       </c>
       <c r="D4" s="5">
-        <v>46127.420010173606</v>
+        <v>46127.58667684028</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1499,13 +1499,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46064.80931388889</v>
+        <v>46064.97598055555</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.57305327547</v>
+        <v>46092.739719942125</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.57308410879</v>
+        <v>46092.739750775465</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1564,13 +1564,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46064.809314212966</v>
+        <v>46064.97598087963</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.57305391204</v>
+        <v>46092.7397205787</v>
       </c>
       <c r="D6" s="5">
-        <v>46092.57308402778</v>
+        <v>46092.73975069444</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1629,13 +1629,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46064.80931452547</v>
+        <v>46064.975981192125</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.57305435185</v>
+        <v>46092.739721018515</v>
       </c>
       <c r="D7" s="8">
-        <v>46092.5730846875</v>
+        <v>46092.739751354165</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -1694,13 +1694,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46064.80931484954</v>
+        <v>46064.9759815162</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.57305482639</v>
+        <v>46092.73972149305</v>
       </c>
       <c r="D8" s="5">
-        <v>46100.62625699074</v>
+        <v>46100.79292365741</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -1759,13 +1759,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46064.80931515046</v>
+        <v>46064.97598181713</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.57305549768</v>
+        <v>46092.73972216435</v>
       </c>
       <c r="D9" s="8">
-        <v>46092.573090370366</v>
+        <v>46092.73975703704</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -1824,13 +1824,13 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46064.80931546296</v>
+        <v>46064.97598212963</v>
       </c>
       <c r="C10" s="5">
-        <v>46198.46686773148</v>
+        <v>46198.63353439815</v>
       </c>
       <c r="D10" s="5">
-        <v>46198.46687005787</v>
+        <v>46198.633536724534</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -1873,13 +1873,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46064.80931575231</v>
+        <v>46064.97598241898</v>
       </c>
       <c r="C11" s="8">
-        <v>46112.484149675925</v>
+        <v>46112.65081634259</v>
       </c>
       <c r="D11" s="8">
-        <v>46112.48417648148</v>
+        <v>46112.65084314815</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -1938,13 +1938,13 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46064.80931606481</v>
+        <v>46064.975982731485</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.61808811342</v>
+        <v>46196.78475478009</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.61809138889</v>
+        <v>46196.78475805555</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2003,13 +2003,13 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46064.80931635416</v>
+        <v>46064.975983020835</v>
       </c>
       <c r="C13" s="8">
-        <v>46114.347010219906</v>
+        <v>46114.51367688658</v>
       </c>
       <c r="D13" s="8">
-        <v>46114.34702380787</v>
+        <v>46114.51369047454</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2056,13 +2056,13 @@
         <v>61</v>
       </c>
       <c r="B14" s="5">
-        <v>46064.809306967596</v>
+        <v>46064.97597363426</v>
       </c>
       <c r="C14" s="5">
-        <v>46111.623314745375</v>
+        <v>46111.78998141203</v>
       </c>
       <c r="D14" s="5">
-        <v>46111.62331697917</v>
+        <v>46111.78998364584</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2121,13 +2121,13 @@
         <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46064.80930760417</v>
+        <v>46064.975974270834</v>
       </c>
       <c r="C15" s="8">
-        <v>46111.62332436343</v>
+        <v>46111.78999103009</v>
       </c>
       <c r="D15" s="8">
-        <v>46111.6233259375</v>
+        <v>46111.78999260417</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>65</v>
@@ -2186,13 +2186,13 @@
         <v>67</v>
       </c>
       <c r="B16" s="5">
-        <v>46064.80930789352</v>
+        <v>46064.975974560184</v>
       </c>
       <c r="C16" s="5">
-        <v>46111.62333570602</v>
+        <v>46111.79000237268</v>
       </c>
       <c r="D16" s="5">
-        <v>46111.623337349534</v>
+        <v>46111.790004016206</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>68</v>
@@ -2251,13 +2251,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="8">
-        <v>46064.80930815972</v>
+        <v>46064.97597482639</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.34699280093</v>
+        <v>46114.51365946759</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.3470103125</v>
+        <v>46114.51367697917</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>71</v>
@@ -2316,13 +2316,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46064.8093084375</v>
+        <v>46064.97597510417</v>
       </c>
       <c r="C18" s="5">
-        <v>46112.48433127315</v>
+        <v>46112.65099793981</v>
       </c>
       <c r="D18" s="5">
-        <v>46139.61509335648</v>
+        <v>46139.78176002315</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2365,13 +2365,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46064.80930898148</v>
+        <v>46064.97597564815</v>
       </c>
       <c r="C19" s="8">
-        <v>46111.623400972225</v>
+        <v>46111.79006763889</v>
       </c>
       <c r="D19" s="8">
-        <v>46111.62341542824</v>
+        <v>46111.79008209491</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2430,13 +2430,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46064.809308703705</v>
+        <v>46064.97597537037</v>
       </c>
       <c r="C20" s="5">
-        <v>46111.62341221065</v>
+        <v>46111.79007887731</v>
       </c>
       <c r="D20" s="5">
-        <v>46111.623428101855</v>
+        <v>46111.79009476852</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -2495,13 +2495,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46064.80930923611</v>
+        <v>46064.97597590278</v>
       </c>
       <c r="C21" s="8">
-        <v>46112.48430203703</v>
+        <v>46112.6509687037</v>
       </c>
       <c r="D21" s="8">
-        <v>46112.48433341435</v>
+        <v>46112.65100008102</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -2560,13 +2560,13 @@
         <v>86</v>
       </c>
       <c r="B22" s="5">
-        <v>46064.809309502314</v>
+        <v>46064.97597616898</v>
       </c>
       <c r="C22" s="5">
-        <v>46111.62344167824</v>
+        <v>46111.79010834491</v>
       </c>
       <c r="D22" s="5">
-        <v>46111.62345855324</v>
+        <v>46111.79012521991</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2625,13 +2625,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46064.80930645834</v>
+        <v>46064.975973125</v>
       </c>
       <c r="C23" s="8">
-        <v>46111.62349084491</v>
+        <v>46111.790157511576</v>
       </c>
       <c r="D23" s="8">
-        <v>46111.62350752315</v>
+        <v>46111.79017418981</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -2690,13 +2690,13 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>46064.80930671297</v>
+        <v>46064.97597337963</v>
       </c>
       <c r="C24" s="5">
-        <v>46114.597614976854</v>
+        <v>46114.76428164352</v>
       </c>
       <c r="D24" s="5">
-        <v>46155.662779502316</v>
+        <v>46155.82944616898</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>96</v>
@@ -2739,13 +2739,13 @@
         <v>98</v>
       </c>
       <c r="B25" s="8">
-        <v>46064.809306967596</v>
+        <v>46064.97597363426</v>
       </c>
       <c r="C25" s="8">
-        <v>46111.62412446759</v>
+        <v>46111.79079113426</v>
       </c>
       <c r="D25" s="8">
-        <v>46139.61514642361</v>
+        <v>46139.781813090274</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>99</v>
@@ -2804,13 +2804,13 @@
         <v>103</v>
       </c>
       <c r="B26" s="5">
-        <v>46064.820425868056</v>
+        <v>46064.98709253472</v>
       </c>
       <c r="C26" s="5">
-        <v>46111.624070405094</v>
+        <v>46111.79073707176</v>
       </c>
       <c r="D26" s="5">
-        <v>46111.62407200232</v>
+        <v>46111.79073866898</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>104</v>
@@ -2859,13 +2859,13 @@
         <v>106</v>
       </c>
       <c r="B27" s="8">
-        <v>46064.82027923611</v>
+        <v>46064.98694590278</v>
       </c>
       <c r="C27" s="8">
-        <v>46111.624109212964</v>
+        <v>46111.79077587963</v>
       </c>
       <c r="D27" s="8">
-        <v>46111.62411060186</v>
+        <v>46111.790777268514</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>107</v>
@@ -2914,13 +2914,13 @@
         <v>109</v>
       </c>
       <c r="B28" s="5">
-        <v>46064.809307812495</v>
+        <v>46064.975974479166</v>
       </c>
       <c r="C28" s="5">
-        <v>46155.66277267361</v>
+        <v>46155.829439340276</v>
       </c>
       <c r="D28" s="5">
-        <v>46155.66284179398</v>
+        <v>46155.82950846065</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>110</v>
@@ -2979,13 +2979,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46064.80930810185</v>
+        <v>46064.97597476852</v>
       </c>
       <c r="C29" s="8">
-        <v>46112.48434800926</v>
+        <v>46112.651014675925</v>
       </c>
       <c r="D29" s="8">
-        <v>46112.48434962963</v>
+        <v>46112.651016296295</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3040,13 +3040,13 @@
         <v>117</v>
       </c>
       <c r="B30" s="5">
-        <v>46064.80930835648</v>
+        <v>46064.975975023146</v>
       </c>
       <c r="C30" s="5">
-        <v>46154.39134616898</v>
+        <v>46154.55801283565</v>
       </c>
       <c r="D30" s="5">
-        <v>46154.39134756944</v>
+        <v>46154.558014236114</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>118</v>
@@ -3101,13 +3101,13 @@
         <v>120</v>
       </c>
       <c r="B31" s="8">
-        <v>46064.80930862269</v>
+        <v>46064.97597528935</v>
       </c>
       <c r="C31" s="8">
-        <v>46111.62398993055</v>
+        <v>46111.79065659722</v>
       </c>
       <c r="D31" s="8">
-        <v>46111.62400064815</v>
+        <v>46111.79066731481</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>121</v>
@@ -3166,13 +3166,13 @@
         <v>123</v>
       </c>
       <c r="B32" s="5">
-        <v>46064.809306180556</v>
+        <v>46064.97597284723</v>
       </c>
       <c r="C32" s="5">
-        <v>46111.62392708333</v>
+        <v>46111.79059375</v>
       </c>
       <c r="D32" s="5">
-        <v>46111.62392899305</v>
+        <v>46111.790595659724</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>124</v>
@@ -3227,13 +3227,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46064.809306574076</v>
+        <v>46064.97597324074</v>
       </c>
       <c r="C33" s="8">
-        <v>46111.62397100695</v>
+        <v>46111.79063767361</v>
       </c>
       <c r="D33" s="8">
-        <v>46111.6239724537</v>
+        <v>46111.79063912037</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>127</v>
@@ -3288,13 +3288,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46064.80930684028</v>
+        <v>46064.975973506946</v>
       </c>
       <c r="C34" s="5">
-        <v>46111.62387822916</v>
+        <v>46111.79054489583</v>
       </c>
       <c r="D34" s="5">
-        <v>46111.623891979165</v>
+        <v>46111.79055864584</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3353,13 +3353,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46064.80930710648</v>
+        <v>46064.97597377315</v>
       </c>
       <c r="C35" s="8">
-        <v>46111.6238140162</v>
+        <v>46111.790480682874</v>
       </c>
       <c r="D35" s="8">
-        <v>46111.62381521991</v>
+        <v>46111.79048188658</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3414,13 +3414,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46064.80930738426</v>
+        <v>46064.975974050925</v>
       </c>
       <c r="C36" s="5">
-        <v>46111.623850648146</v>
+        <v>46111.79051731482</v>
       </c>
       <c r="D36" s="5">
-        <v>46111.62385216435</v>
+        <v>46111.79051883102</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3475,13 +3475,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46064.80930765046</v>
+        <v>46064.97597431713</v>
       </c>
       <c r="C37" s="8">
-        <v>46111.62386230324</v>
+        <v>46111.79052896991</v>
       </c>
       <c r="D37" s="8">
-        <v>46111.62386381945</v>
+        <v>46111.79053048611</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3536,13 +3536,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46064.80930792824</v>
+        <v>46064.97597459491</v>
       </c>
       <c r="C38" s="5">
-        <v>46111.62376377315</v>
+        <v>46111.79043043981</v>
       </c>
       <c r="D38" s="5">
-        <v>46139.61517496528</v>
+        <v>46139.78184163195</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3601,13 +3601,13 @@
         <v>145</v>
       </c>
       <c r="B39" s="8">
-        <v>46064.80930820602</v>
+        <v>46064.97597487269</v>
       </c>
       <c r="C39" s="8">
-        <v>46111.62370167824</v>
+        <v>46111.79036834491</v>
       </c>
       <c r="D39" s="8">
-        <v>46111.62370304398</v>
+        <v>46111.79036971065</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3662,13 +3662,13 @@
         <v>148</v>
       </c>
       <c r="B40" s="5">
-        <v>46064.8093084838</v>
+        <v>46064.97597515046</v>
       </c>
       <c r="C40" s="5">
-        <v>46111.6237495949</v>
+        <v>46111.790416261574</v>
       </c>
       <c r="D40" s="5">
-        <v>46111.62375113426</v>
+        <v>46111.79041780093</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -3723,13 +3723,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46064.809307881944</v>
+        <v>46064.97597454861</v>
       </c>
       <c r="C41" s="8">
-        <v>46114.60195364583</v>
+        <v>46114.768620312505</v>
       </c>
       <c r="D41" s="8">
-        <v>46139.61497306713</v>
+        <v>46139.781639733796</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -3772,13 +3772,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46070.50289251158</v>
+        <v>46070.66955917824</v>
       </c>
       <c r="C42" s="5">
-        <v>46114.34715076389</v>
+        <v>46114.513817430554</v>
       </c>
       <c r="D42" s="5">
-        <v>46114.34716959491</v>
+        <v>46114.51383626157</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -3837,13 +3837,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46064.8093081713</v>
+        <v>46064.97597483796</v>
       </c>
       <c r="C43" s="8">
-        <v>46114.347206666665</v>
+        <v>46114.51387333333</v>
       </c>
       <c r="D43" s="8">
-        <v>46114.3472219213</v>
+        <v>46114.513888587964</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -3902,13 +3902,13 @@
         <v>162</v>
       </c>
       <c r="B44" s="5">
-        <v>46087.336886377314</v>
+        <v>46087.50355304398</v>
       </c>
       <c r="C44" s="5">
-        <v>46114.34725474537</v>
+        <v>46114.513921412035</v>
       </c>
       <c r="D44" s="5">
-        <v>46114.347268784724</v>
+        <v>46114.51393545139</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>163</v>
@@ -3967,13 +3967,13 @@
         <v>165</v>
       </c>
       <c r="B45" s="8">
-        <v>46087.3369296412</v>
+        <v>46087.50359630787</v>
       </c>
       <c r="C45" s="8">
-        <v>46114.6019366088</v>
+        <v>46114.768603275465</v>
       </c>
       <c r="D45" s="8">
-        <v>46127.014816875</v>
+        <v>46127.181483541666</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>166</v>
@@ -4030,13 +4030,13 @@
         <v>171</v>
       </c>
       <c r="B46" s="5">
-        <v>46064.80930847222</v>
+        <v>46064.97597513889</v>
       </c>
       <c r="C46" s="5">
-        <v>46107.54886012731</v>
+        <v>46107.71552679398</v>
       </c>
       <c r="D46" s="5">
-        <v>46139.61487302084</v>
+        <v>46139.7815396875</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>172</v>
@@ -4079,13 +4079,13 @@
         <v>174</v>
       </c>
       <c r="B47" s="8">
-        <v>46064.80930877315</v>
+        <v>46064.97597543981</v>
       </c>
       <c r="C47" s="8">
-        <v>46107.54884430555</v>
+        <v>46107.71551097222</v>
       </c>
       <c r="D47" s="8">
-        <v>46139.61481119213</v>
+        <v>46139.78147785879</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>149</v>
@@ -4144,13 +4144,13 @@
         <v>178</v>
       </c>
       <c r="B48" s="5">
-        <v>46064.809309062504</v>
+        <v>46064.97597572916</v>
       </c>
       <c r="C48" s="5">
-        <v>46107.548765451385</v>
+        <v>46107.71543211806</v>
       </c>
       <c r="D48" s="5">
-        <v>46139.61483048611</v>
+        <v>46139.78149715278</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>179</v>
@@ -4209,13 +4209,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46064.80930936342</v>
+        <v>46064.975976030095</v>
       </c>
       <c r="C49" s="8">
-        <v>46107.54899877315</v>
+        <v>46107.71566543981</v>
       </c>
       <c r="D49" s="8">
-        <v>46139.61478167824</v>
+        <v>46139.781448344904</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4258,13 +4258,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46064.809309652774</v>
+        <v>46064.975976319445</v>
       </c>
       <c r="C50" s="5">
-        <v>46107.5485365625</v>
+        <v>46107.71520322916</v>
       </c>
       <c r="D50" s="5">
-        <v>46139.61468195602</v>
+        <v>46139.78134862268</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4323,13 +4323,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46064.80931</v>
+        <v>46064.97597666667</v>
       </c>
       <c r="C51" s="8">
-        <v>46107.54864957176</v>
+        <v>46107.71531623843</v>
       </c>
       <c r="D51" s="8">
-        <v>46139.61470181713</v>
+        <v>46139.7813684838</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4388,13 +4388,13 @@
         <v>195</v>
       </c>
       <c r="B52" s="5">
-        <v>46064.80930681713</v>
+        <v>46064.9759734838</v>
       </c>
       <c r="C52" s="5">
-        <v>46107.548982719905</v>
+        <v>46107.71564938658</v>
       </c>
       <c r="D52" s="5">
-        <v>46139.61473543981</v>
+        <v>46139.781402106484</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>196</v>
@@ -4451,13 +4451,13 @@
         <v>199</v>
       </c>
       <c r="B53" s="8">
-        <v>46064.80930719907</v>
+        <v>46064.975973865745</v>
       </c>
       <c r="C53" s="8">
-        <v>46155.66268663194</v>
+        <v>46155.82935329861</v>
       </c>
       <c r="D53" s="8">
-        <v>46155.66268811343</v>
+        <v>46155.82935478009</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>172</v>
@@ -4500,13 +4500,13 @@
         <v>201</v>
       </c>
       <c r="B54" s="5">
-        <v>46064.80930784722</v>
+        <v>46064.97597451389</v>
       </c>
       <c r="C54" s="5">
-        <v>46107.54818842592</v>
+        <v>46107.71485509259</v>
       </c>
       <c r="D54" s="5">
-        <v>46139.61443797454</v>
+        <v>46139.7811046412</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>202</v>
@@ -4563,13 +4563,13 @@
         <v>204</v>
       </c>
       <c r="B55" s="8">
-        <v>46064.809308449076</v>
+        <v>46064.97597511574</v>
       </c>
       <c r="C55" s="8">
-        <v>46154.39139984954</v>
+        <v>46154.558066516205</v>
       </c>
       <c r="D55" s="8">
-        <v>46155.66287702546</v>
+        <v>46155.82954369213</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>56</v>
@@ -4626,13 +4626,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46064.809307557865</v>
+        <v>46064.97597422454</v>
       </c>
       <c r="C56" s="5">
-        <v>46107.548039201385</v>
+        <v>46107.71470586806</v>
       </c>
       <c r="D56" s="5">
-        <v>46139.614411400464</v>
+        <v>46139.78107806713</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -4689,13 +4689,13 @@
         <v>209</v>
       </c>
       <c r="B57" s="8">
-        <v>46065.338309212966</v>
+        <v>46065.50497587963</v>
       </c>
       <c r="C57" s="8">
-        <v>46107.547905416664</v>
+        <v>46107.714572083336</v>
       </c>
       <c r="D57" s="8">
-        <v>46139.614389594906</v>
+        <v>46139.78105626158</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>210</v>
@@ -4752,13 +4752,13 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46064.809308993055</v>
+        <v>46064.97597565972</v>
       </c>
       <c r="C58" s="5">
-        <v>46107.548378391206</v>
+        <v>46107.71504505787</v>
       </c>
       <c r="D58" s="5">
-        <v>46139.61459003472</v>
+        <v>46139.78125670139</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -4801,13 +4801,13 @@
         <v>215</v>
       </c>
       <c r="B59" s="8">
-        <v>46064.80930925926</v>
+        <v>46064.975975925925</v>
       </c>
       <c r="C59" s="8">
-        <v>46107.54835604166</v>
+        <v>46107.71502270833</v>
       </c>
       <c r="D59" s="8">
-        <v>46120.00679005787</v>
+        <v>46120.17345672454</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>216</v>
@@ -4866,13 +4866,13 @@
         <v>218</v>
       </c>
       <c r="B60" s="5">
-        <v>46064.80930957176</v>
+        <v>46064.97597623843</v>
       </c>
       <c r="C60" s="5">
-        <v>46107.54703266204</v>
+        <v>46107.7136993287</v>
       </c>
       <c r="D60" s="5">
-        <v>46139.61447259259</v>
+        <v>46139.781139259256</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -4929,13 +4929,13 @@
         <v>221</v>
       </c>
       <c r="B61" s="8">
-        <v>46064.80930677083</v>
+        <v>46064.9759734375</v>
       </c>
       <c r="C61" s="8">
-        <v>46107.54724788194</v>
+        <v>46107.713914548614</v>
       </c>
       <c r="D61" s="8">
-        <v>46139.61449416667</v>
+        <v>46139.78116083333</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>222</v>
@@ -4992,13 +4992,13 @@
         <v>224</v>
       </c>
       <c r="B62" s="5">
-        <v>46064.80930710648</v>
+        <v>46064.97597377315</v>
       </c>
       <c r="C62" s="5">
-        <v>46107.547382916666</v>
+        <v>46107.71404958333</v>
       </c>
       <c r="D62" s="5">
-        <v>46139.614516898146</v>
+        <v>46139.78118356482</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>225</v>
@@ -5055,13 +5055,13 @@
         <v>227</v>
       </c>
       <c r="B63" s="8">
-        <v>46064.809307627314</v>
+        <v>46064.97597429398</v>
       </c>
       <c r="C63" s="8">
-        <v>46107.547501354165</v>
+        <v>46107.71416802083</v>
       </c>
       <c r="D63" s="8">
-        <v>46126.04068769676</v>
+        <v>46126.207354363425</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>169</v>
@@ -5118,13 +5118,13 @@
         <v>230</v>
       </c>
       <c r="B64" s="5">
-        <v>46064.809307881944</v>
+        <v>46064.97597454861</v>
       </c>
       <c r="C64" s="5">
-        <v>46107.54765474537</v>
+        <v>46107.71432141204</v>
       </c>
       <c r="D64" s="5">
-        <v>46139.614540243056</v>
+        <v>46139.78120690973</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>231</v>
@@ -5181,13 +5181,13 @@
         <v>233</v>
       </c>
       <c r="B65" s="8">
-        <v>46064.809308125</v>
+        <v>46064.97597479167</v>
       </c>
       <c r="C65" s="8">
-        <v>46198.467189965275</v>
+        <v>46198.63385663195</v>
       </c>
       <c r="D65" s="8">
-        <v>46198.467191331016</v>
+        <v>46198.63385799769</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>234</v>
@@ -5230,13 +5230,13 @@
         <v>236</v>
       </c>
       <c r="B66" s="5">
-        <v>46064.80930837963</v>
+        <v>46064.9759750463</v>
       </c>
       <c r="C66" s="5">
-        <v>46197.41720766204</v>
+        <v>46197.5838743287</v>
       </c>
       <c r="D66" s="5">
-        <v>46198.467289513894</v>
+        <v>46198.63395618055</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>237</v>
@@ -5293,13 +5293,13 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46064.80930862269</v>
+        <v>46064.97597528935</v>
       </c>
       <c r="C67" s="8">
-        <v>46197.54342800926</v>
+        <v>46197.71009467593</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.46729019676</v>
+        <v>46198.63395686343</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5356,13 +5356,13 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46064.80930886574</v>
+        <v>46064.975975532405</v>
       </c>
       <c r="C68" s="5">
-        <v>46197.54351621528</v>
+        <v>46197.71018288194</v>
       </c>
       <c r="D68" s="5">
-        <v>46198.46729078704</v>
+        <v>46198.633957453705</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5419,13 +5419,13 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46064.80930912037</v>
+        <v>46064.975975787034</v>
       </c>
       <c r="C69" s="8">
-        <v>46197.54355560185</v>
+        <v>46197.71022226852</v>
       </c>
       <c r="D69" s="8">
-        <v>46198.467291423614</v>
+        <v>46198.63395809028</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>251</v>
@@ -5482,11 +5482,11 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46064.80930690972</v>
+        <v>46064.97597357639</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.62547358796</v>
+        <v>46126.792140254634</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>254</v>
@@ -5529,11 +5529,11 @@
         <v>256</v>
       </c>
       <c r="B71" s="8">
-        <v>46064.80930769676</v>
+        <v>46064.97597436343</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46197.54356501157</v>
+        <v>46197.71023167824</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>257</v>
@@ -5592,11 +5592,11 @@
         <v>260</v>
       </c>
       <c r="B72" s="5">
-        <v>46064.80930738426</v>
+        <v>46064.975974050925</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46197.543566458335</v>
+        <v>46197.710233125</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>261</v>
@@ -5655,13 +5655,13 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.3650941088</v>
+        <v>46090.53176077546</v>
       </c>
       <c r="C73" s="8">
-        <v>46198.46717871528</v>
+        <v>46198.63384538195</v>
       </c>
       <c r="D73" s="8">
-        <v>46198.467180127314</v>
+        <v>46198.63384679398</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>264</v>
@@ -5704,13 +5704,13 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.366989016205</v>
+        <v>46090.53365568287</v>
       </c>
       <c r="C74" s="5">
-        <v>46198.46698320602</v>
+        <v>46198.63364987269</v>
       </c>
       <c r="D74" s="5">
-        <v>46198.46720513889</v>
+        <v>46198.633871805556</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>267</v>
@@ -5769,13 +5769,13 @@
         <v>269</v>
       </c>
       <c r="B75" s="8">
-        <v>46090.3671906713</v>
+        <v>46090.53385733796</v>
       </c>
       <c r="C75" s="8">
-        <v>46198.46710174769</v>
+        <v>46198.63376841435</v>
       </c>
       <c r="D75" s="8">
-        <v>46198.46723030093</v>
+        <v>46198.63389696759</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>270</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -5486,7 +5486,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46126.792140254634</v>
+        <v>46213.83018092593</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>254</v>
@@ -5531,9 +5531,11 @@
       <c r="B71" s="8">
         <v>46064.97597436343</v>
       </c>
-      <c r="C71" s="9"/>
+      <c r="C71" s="8">
+        <v>46213.83015892361</v>
+      </c>
       <c r="D71" s="8">
-        <v>46197.71023167824</v>
+        <v>46213.830161307866</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>257</v>
@@ -5594,9 +5596,11 @@
       <c r="B72" s="5">
         <v>46064.975974050925</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46213.83017385416</v>
+      </c>
       <c r="D72" s="5">
-        <v>46197.710233125</v>
+        <v>46213.83017636574</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>261</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="268">
   <si>
     <t>50001514 - CLIENTE POR DEFINIR</t>
   </si>
@@ -277,9 +277,6 @@
     <t>propuesta nucleo rodete</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
   </si>
   <si>
@@ -287,12 +284,6 @@
   </si>
   <si>
     <t>propuesta compras a codigo // aprovisionamiento</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC materiales</t>
@@ -2575,11 +2566,9 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>46062</v>
       </c>
@@ -2602,7 +2591,7 @@
         <v>65</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q22" s="5">
         <v>46063</v>
@@ -2622,7 +2611,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="8">
         <v>46064.975973125</v>
@@ -2634,17 +2623,15 @@
         <v>46111.79017418981</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>93</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H23" s="9"/>
       <c r="I23" s="8">
         <v>46063</v>
       </c>
@@ -2667,7 +2654,7 @@
         <v>68</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="Q23" s="8">
         <v>46064</v>
@@ -2687,7 +2674,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B24" s="5">
         <v>46064.97597337963</v>
@@ -2699,7 +2686,7 @@
         <v>46155.82944616898</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>25</v>
@@ -2723,7 +2710,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2736,7 +2723,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B25" s="8">
         <v>46064.97597363426</v>
@@ -2748,16 +2735,16 @@
         <v>46139.781813090274</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I25" s="8">
         <v>46064</v>
@@ -2775,13 +2762,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q25" s="8">
         <v>46069</v>
@@ -2801,7 +2788,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B26" s="5">
         <v>46064.98709253472</v>
@@ -2813,16 +2800,16 @@
         <v>46111.79073866898</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I26" s="5">
         <v>46064</v>
@@ -2840,13 +2827,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2856,7 +2843,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B27" s="8">
         <v>46064.98694590278</v>
@@ -2868,16 +2855,16 @@
         <v>46111.790777268514</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I27" s="8">
         <v>46066</v>
@@ -2895,13 +2882,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2911,7 +2898,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B28" s="5">
         <v>46064.975974479166</v>
@@ -2923,16 +2910,16 @@
         <v>46155.82950846065</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I28" s="5">
         <v>46064</v>
@@ -2950,13 +2937,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q28" s="5">
         <v>46121</v>
@@ -2976,7 +2963,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B29" s="8">
         <v>46064.97597476852</v>
@@ -2988,16 +2975,16 @@
         <v>46112.651016296295</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I29" s="8">
         <v>46064</v>
@@ -3015,13 +3002,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3029,15 +3016,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5">
         <v>46064.975975023146</v>
@@ -3049,16 +3036,16 @@
         <v>46154.558014236114</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I30" s="5">
         <v>46073</v>
@@ -3076,13 +3063,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="O30" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3090,15 +3077,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B31" s="8">
         <v>46064.97597528935</v>
@@ -3110,16 +3097,16 @@
         <v>46111.79066731481</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I31" s="8">
         <v>46064</v>
@@ -3137,13 +3124,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q31" s="8">
         <v>46084</v>
@@ -3163,7 +3150,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5">
         <v>46064.97597284723</v>
@@ -3175,16 +3162,16 @@
         <v>46111.790595659724</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I32" s="5">
         <v>46064</v>
@@ -3202,13 +3189,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3216,15 +3203,15 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B33" s="8">
         <v>46064.97597324074</v>
@@ -3236,16 +3223,16 @@
         <v>46111.79063912037</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I33" s="8">
         <v>46065</v>
@@ -3263,13 +3250,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="O33" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3277,15 +3264,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46064.975973506946</v>
@@ -3297,16 +3284,16 @@
         <v>46111.79055864584</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I34" s="5">
         <v>46064</v>
@@ -3324,13 +3311,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q34" s="5">
         <v>46101</v>
@@ -3350,7 +3337,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46064.97597377315</v>
@@ -3362,16 +3349,16 @@
         <v>46111.79048188658</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I35" s="8">
         <v>46064</v>
@@ -3389,13 +3376,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>81</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3403,15 +3390,15 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46064.975974050925</v>
@@ -3423,16 +3410,16 @@
         <v>46111.79051883102</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I36" s="5">
         <v>46073</v>
@@ -3450,13 +3437,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="O36" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="O36" s="6" t="s">
-        <v>133</v>
-      </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3464,15 +3451,15 @@
         <v>0</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46064.97597431713</v>
@@ -3484,16 +3471,16 @@
         <v>46111.79053048611</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I37" s="8">
         <v>46073</v>
@@ -3511,13 +3498,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="O37" s="9" t="s">
-        <v>133</v>
-      </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3525,15 +3512,15 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46064.97597459491</v>
@@ -3545,16 +3532,16 @@
         <v>46139.78184163195</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I38" s="5">
         <v>46065</v>
@@ -3572,13 +3559,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q38" s="5">
         <v>46091</v>
@@ -3598,7 +3585,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B39" s="8">
         <v>46064.97597487269</v>
@@ -3610,16 +3597,16 @@
         <v>46111.79036971065</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I39" s="8">
         <v>46065</v>
@@ -3637,13 +3624,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3651,15 +3638,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46064.97597515046</v>
@@ -3671,16 +3658,16 @@
         <v>46111.79041780093</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I40" s="5">
         <v>46076</v>
@@ -3698,13 +3685,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O40" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="P40" s="6" t="s">
         <v>146</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3712,15 +3699,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46064.97597454861</v>
@@ -3732,7 +3719,7 @@
         <v>46139.781639733796</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>25</v>
@@ -3756,7 +3743,7 @@
         <v>26</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -3769,7 +3756,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46070.66955917824</v>
@@ -3781,16 +3768,16 @@
         <v>46114.51383626157</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I42" s="5">
         <v>46063</v>
@@ -3808,13 +3795,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q42" s="5">
         <v>46069</v>
@@ -3834,7 +3821,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B43" s="8">
         <v>46064.97597483796</v>
@@ -3846,16 +3833,16 @@
         <v>46114.513888587964</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I43" s="8">
         <v>46084</v>
@@ -3873,13 +3860,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="8">
         <v>46090</v>
@@ -3899,7 +3886,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46087.50355304398</v>
@@ -3911,16 +3898,16 @@
         <v>46114.51393545139</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I44" s="5">
         <v>46091</v>
@@ -3938,13 +3925,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="Q44" s="5">
         <v>46091</v>
@@ -3964,7 +3951,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46087.50359630787</v>
@@ -3976,16 +3963,16 @@
         <v>46127.181483541666</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -4001,13 +3988,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="8">
         <v>46126</v>
@@ -4027,7 +4014,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46064.97597513889</v>
@@ -4039,7 +4026,7 @@
         <v>46139.7815396875</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4063,7 +4050,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4076,7 +4063,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46064.97597543981</v>
@@ -4088,16 +4075,16 @@
         <v>46139.78147785879</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I47" s="8">
         <v>46094</v>
@@ -4115,13 +4102,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="8">
         <v>46097</v>
@@ -4141,7 +4128,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46064.97597572916</v>
@@ -4153,16 +4140,16 @@
         <v>46139.78149715278</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46098</v>
@@ -4180,13 +4167,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="5">
         <v>46099</v>
@@ -4206,7 +4193,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46064.975976030095</v>
@@ -4218,7 +4205,7 @@
         <v>46139.781448344904</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>25</v>
@@ -4242,7 +4229,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4255,7 +4242,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B50" s="5">
         <v>46064.975976319445</v>
@@ -4267,16 +4254,16 @@
         <v>46139.78134862268</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I50" s="5">
         <v>46100</v>
@@ -4294,13 +4281,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="Q50" s="5">
         <v>46104</v>
@@ -4320,7 +4307,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B51" s="8">
         <v>46064.97597666667</v>
@@ -4332,16 +4319,16 @@
         <v>46139.7813684838</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I51" s="8">
         <v>46105</v>
@@ -4359,13 +4346,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="8">
         <v>46111</v>
@@ -4385,7 +4372,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46064.9759734838</v>
@@ -4397,16 +4384,16 @@
         <v>46139.781402106484</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4422,13 +4409,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="5">
         <v>46112</v>
@@ -4448,7 +4435,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B53" s="8">
         <v>46064.975973865745</v>
@@ -4460,7 +4447,7 @@
         <v>46155.82935478009</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4484,7 +4471,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4497,7 +4484,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46064.97597451389</v>
@@ -4509,16 +4496,16 @@
         <v>46139.7811046412</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4534,13 +4521,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46085</v>
@@ -4560,7 +4547,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B55" s="8">
         <v>46064.97597511574</v>
@@ -4578,10 +4565,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4597,13 +4584,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="Q55" s="8">
         <v>46122</v>
@@ -4623,7 +4610,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B56" s="5">
         <v>46064.97597422454</v>
@@ -4635,16 +4622,16 @@
         <v>46139.78107806713</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -4660,13 +4647,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="Q56" s="5">
         <v>46070</v>
@@ -4686,7 +4673,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B57" s="8">
         <v>46065.50497587963</v>
@@ -4698,16 +4685,16 @@
         <v>46139.78105626158</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -4723,13 +4710,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="Q57" s="8">
         <v>46104</v>
@@ -4749,7 +4736,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B58" s="5">
         <v>46064.97597565972</v>
@@ -4761,7 +4748,7 @@
         <v>46139.78125670139</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4785,7 +4772,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4798,7 +4785,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B59" s="8">
         <v>46064.975975925925</v>
@@ -4810,17 +4797,15 @@
         <v>46120.17345672454</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H59" s="9"/>
       <c r="I59" s="8">
         <v>46113</v>
       </c>
@@ -4837,13 +4822,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Q59" s="8">
         <v>46119</v>
@@ -4863,7 +4848,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B60" s="5">
         <v>46064.97597623843</v>
@@ -4875,17 +4860,15 @@
         <v>46139.781139259256</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H60" s="6"/>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
         <v>46120</v>
@@ -4900,13 +4883,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q60" s="5">
         <v>46118</v>
@@ -4926,7 +4909,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B61" s="8">
         <v>46064.9759734375</v>
@@ -4938,17 +4921,15 @@
         <v>46139.78116083333</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H61" s="9"/>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
         <v>46121</v>
@@ -4963,13 +4944,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q61" s="8">
         <v>46119</v>
@@ -4989,7 +4970,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B62" s="5">
         <v>46064.97597377315</v>
@@ -5001,17 +4982,15 @@
         <v>46139.78118356482</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H62" s="6"/>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
         <v>46122</v>
@@ -5026,13 +5005,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q62" s="5">
         <v>46122</v>
@@ -5052,7 +5031,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B63" s="8">
         <v>46064.97597429398</v>
@@ -5064,17 +5043,15 @@
         <v>46126.207354363425</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H63" s="9"/>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
         <v>46125</v>
@@ -5089,13 +5066,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q63" s="8">
         <v>46125</v>
@@ -5115,7 +5092,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B64" s="5">
         <v>46064.97597454861</v>
@@ -5127,17 +5104,15 @@
         <v>46139.78120690973</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H64" s="6"/>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
         <v>46127</v>
@@ -5152,13 +5127,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q64" s="5">
         <v>46127</v>
@@ -5178,7 +5153,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B65" s="8">
         <v>46064.97597479167</v>
@@ -5190,7 +5165,7 @@
         <v>46198.63385799769</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5214,7 +5189,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5227,7 +5202,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B66" s="5">
         <v>46064.9759750463</v>
@@ -5239,16 +5214,16 @@
         <v>46198.63395618055</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5264,13 +5239,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="Q66" s="5">
         <v>46135</v>
@@ -5285,12 +5260,12 @@
         <v>31</v>
       </c>
       <c r="U66" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B67" s="8">
         <v>46064.97597528935</v>
@@ -5302,17 +5277,15 @@
         <v>46198.63395686343</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>88</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
         <v>46136</v>
@@ -5327,13 +5300,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Q67" s="8">
         <v>46136</v>
@@ -5348,12 +5321,12 @@
         <v>31</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46064.975975532405</v>
@@ -5365,16 +5338,16 @@
         <v>46198.633957453705</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5390,13 +5363,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q68" s="5">
         <v>46139</v>
@@ -5408,15 +5381,15 @@
         <v>1</v>
       </c>
       <c r="T68" s="12" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="U68" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B69" s="8">
         <v>46064.975975787034</v>
@@ -5428,16 +5401,16 @@
         <v>46198.63395809028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5453,13 +5426,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Q69" s="8">
         <v>46140</v>
@@ -5471,15 +5444,15 @@
         <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B70" s="5">
         <v>46064.97597357639</v>
@@ -5489,7 +5462,7 @@
         <v>46213.83018092593</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5513,7 +5486,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5526,7 +5499,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B71" s="8">
         <v>46064.97597436343</v>
@@ -5538,16 +5511,16 @@
         <v>46213.830161307866</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I71" s="8">
         <v>46142</v>
@@ -5565,13 +5538,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O71" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>251</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>254</v>
       </c>
       <c r="Q71" s="8">
         <v>46150</v>
@@ -5583,15 +5556,15 @@
         <v>0</v>
       </c>
       <c r="T71" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B72" s="5">
         <v>46064.975974050925</v>
@@ -5603,16 +5576,16 @@
         <v>46213.83017636574</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I72" s="5">
         <v>46142</v>
@@ -5630,13 +5603,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="Q72" s="5">
         <v>46150</v>
@@ -5648,15 +5621,15 @@
         <v>0</v>
       </c>
       <c r="T72" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B73" s="8">
         <v>46090.53176077546</v>
@@ -5668,7 +5641,7 @@
         <v>46198.63384679398</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5692,7 +5665,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5705,7 +5678,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B74" s="5">
         <v>46090.53365568287</v>
@@ -5717,7 +5690,7 @@
         <v>46198.633871805556</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5744,13 +5717,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Q74" s="5">
         <v>46149</v>
@@ -5762,15 +5735,15 @@
         <v>1</v>
       </c>
       <c r="T74" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B75" s="8">
         <v>46090.53385733796</v>
@@ -5782,7 +5755,7 @@
         <v>46198.63389696759</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5809,13 +5782,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="O75" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="O75" s="9" t="s">
-        <v>267</v>
-      </c>
       <c r="P75" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q75" s="8">
         <v>46161</v>
@@ -5827,10 +5800,10 @@
         <v>1</v>
       </c>
       <c r="T75" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -5457,9 +5457,11 @@
       <c r="B70" s="5">
         <v>46064.97597357639</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46223.62815204861</v>
+      </c>
       <c r="D70" s="5">
-        <v>46213.83018092593</v>
+        <v>46223.628154502316</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>251</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="269">
   <si>
     <t>50001514 - CLIENTE POR DEFINIR</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Generación OC Rodete</t>
@@ -2557,7 +2560,7 @@
         <v>46111.79010834491</v>
       </c>
       <c r="D22" s="5">
-        <v>46111.79012521991</v>
+        <v>46223.834606944445</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -2566,9 +2569,11 @@
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="I22" s="5">
         <v>46062</v>
       </c>
@@ -2591,7 +2596,7 @@
         <v>65</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="5">
         <v>46063</v>
@@ -2611,7 +2616,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="8">
         <v>46064.975973125</v>
@@ -2620,18 +2625,20 @@
         <v>46111.790157511576</v>
       </c>
       <c r="D23" s="8">
-        <v>46111.79017418981</v>
+        <v>46223.834713020835</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="I23" s="8">
         <v>46063</v>
       </c>
@@ -2654,7 +2661,7 @@
         <v>68</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="8">
         <v>46064</v>
@@ -2674,7 +2681,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46064.97597337963</v>
@@ -2686,7 +2693,7 @@
         <v>46155.82944616898</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>25</v>
@@ -2710,7 +2717,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2723,7 +2730,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8">
         <v>46064.97597363426</v>
@@ -2735,16 +2742,16 @@
         <v>46139.781813090274</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I25" s="8">
         <v>46064</v>
@@ -2762,13 +2769,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q25" s="8">
         <v>46069</v>
@@ -2788,7 +2795,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B26" s="5">
         <v>46064.98709253472</v>
@@ -2800,16 +2807,16 @@
         <v>46111.79073866898</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46064</v>
@@ -2827,13 +2834,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2843,7 +2850,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B27" s="8">
         <v>46064.98694590278</v>
@@ -2855,16 +2862,16 @@
         <v>46111.790777268514</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I27" s="8">
         <v>46066</v>
@@ -2882,13 +2889,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2898,7 +2905,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" s="5">
         <v>46064.975974479166</v>
@@ -2910,16 +2917,16 @@
         <v>46155.82950846065</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46064</v>
@@ -2937,13 +2944,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q28" s="5">
         <v>46121</v>
@@ -2963,7 +2970,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B29" s="8">
         <v>46064.97597476852</v>
@@ -2975,16 +2982,16 @@
         <v>46112.651016296295</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I29" s="8">
         <v>46064</v>
@@ -3002,13 +3009,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3016,15 +3023,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46064.975975023146</v>
@@ -3036,16 +3043,16 @@
         <v>46154.558014236114</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46073</v>
@@ -3063,13 +3070,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3077,15 +3084,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46064.97597528935</v>
@@ -3097,16 +3104,16 @@
         <v>46111.79066731481</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I31" s="8">
         <v>46064</v>
@@ -3124,13 +3131,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q31" s="8">
         <v>46084</v>
@@ -3150,7 +3157,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46064.97597284723</v>
@@ -3162,16 +3169,16 @@
         <v>46111.790595659724</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I32" s="5">
         <v>46064</v>
@@ -3189,13 +3196,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3203,15 +3210,15 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B33" s="8">
         <v>46064.97597324074</v>
@@ -3223,16 +3230,16 @@
         <v>46111.79063912037</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I33" s="8">
         <v>46065</v>
@@ -3250,13 +3257,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3264,15 +3271,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46064.975973506946</v>
@@ -3284,16 +3291,16 @@
         <v>46111.79055864584</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I34" s="5">
         <v>46064</v>
@@ -3311,13 +3318,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q34" s="5">
         <v>46101</v>
@@ -3337,7 +3344,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46064.97597377315</v>
@@ -3349,16 +3356,16 @@
         <v>46111.79048188658</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I35" s="8">
         <v>46064</v>
@@ -3376,13 +3383,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>81</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3390,15 +3397,15 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46064.975974050925</v>
@@ -3410,16 +3417,16 @@
         <v>46111.79051883102</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I36" s="5">
         <v>46073</v>
@@ -3437,13 +3444,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3451,15 +3458,15 @@
         <v>0</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46064.97597431713</v>
@@ -3471,16 +3478,16 @@
         <v>46111.79053048611</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I37" s="8">
         <v>46073</v>
@@ -3498,13 +3505,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3512,15 +3519,15 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46064.97597459491</v>
@@ -3532,16 +3539,16 @@
         <v>46139.78184163195</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I38" s="5">
         <v>46065</v>
@@ -3559,13 +3566,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q38" s="5">
         <v>46091</v>
@@ -3585,7 +3592,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46064.97597487269</v>
@@ -3597,16 +3604,16 @@
         <v>46111.79036971065</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I39" s="8">
         <v>46065</v>
@@ -3624,13 +3631,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3638,15 +3645,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46064.97597515046</v>
@@ -3658,16 +3665,16 @@
         <v>46111.79041780093</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I40" s="5">
         <v>46076</v>
@@ -3685,13 +3692,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3699,15 +3706,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B41" s="8">
         <v>46064.97597454861</v>
@@ -3719,7 +3726,7 @@
         <v>46139.781639733796</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>25</v>
@@ -3743,7 +3750,7 @@
         <v>26</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -3756,7 +3763,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46070.66955917824</v>
@@ -3768,16 +3775,16 @@
         <v>46114.51383626157</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46063</v>
@@ -3795,13 +3802,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q42" s="5">
         <v>46069</v>
@@ -3821,7 +3828,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46064.97597483796</v>
@@ -3833,16 +3840,16 @@
         <v>46114.513888587964</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I43" s="8">
         <v>46084</v>
@@ -3860,13 +3867,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="8">
         <v>46090</v>
@@ -3886,7 +3893,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46087.50355304398</v>
@@ -3898,16 +3905,16 @@
         <v>46114.51393545139</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46091</v>
@@ -3925,13 +3932,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="5">
         <v>46091</v>
@@ -3951,7 +3958,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46087.50359630787</v>
@@ -3963,16 +3970,16 @@
         <v>46127.181483541666</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -3988,13 +3995,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q45" s="8">
         <v>46126</v>
@@ -4014,7 +4021,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5">
         <v>46064.97597513889</v>
@@ -4026,7 +4033,7 @@
         <v>46139.7815396875</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4050,7 +4057,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4063,7 +4070,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46064.97597543981</v>
@@ -4075,16 +4082,16 @@
         <v>46139.78147785879</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46094</v>
@@ -4102,13 +4109,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q47" s="8">
         <v>46097</v>
@@ -4128,7 +4135,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46064.97597572916</v>
@@ -4140,16 +4147,16 @@
         <v>46139.78149715278</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I48" s="5">
         <v>46098</v>
@@ -4167,13 +4174,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="5">
         <v>46099</v>
@@ -4193,7 +4200,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="8">
         <v>46064.975976030095</v>
@@ -4205,7 +4212,7 @@
         <v>46139.781448344904</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>25</v>
@@ -4229,7 +4236,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4242,7 +4249,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46064.975976319445</v>
@@ -4254,16 +4261,16 @@
         <v>46139.78134862268</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I50" s="5">
         <v>46100</v>
@@ -4281,13 +4288,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q50" s="5">
         <v>46104</v>
@@ -4307,7 +4314,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8">
         <v>46064.97597666667</v>
@@ -4319,16 +4326,16 @@
         <v>46139.7813684838</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I51" s="8">
         <v>46105</v>
@@ -4346,13 +4353,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q51" s="8">
         <v>46111</v>
@@ -4372,7 +4379,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="5">
         <v>46064.9759734838</v>
@@ -4384,16 +4391,16 @@
         <v>46139.781402106484</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4409,13 +4416,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q52" s="5">
         <v>46112</v>
@@ -4435,7 +4442,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B53" s="8">
         <v>46064.975973865745</v>
@@ -4447,7 +4454,7 @@
         <v>46155.82935478009</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4471,7 +4478,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4484,7 +4491,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46064.97597451389</v>
@@ -4496,16 +4503,16 @@
         <v>46139.7811046412</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4521,13 +4528,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46085</v>
@@ -4547,7 +4554,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="8">
         <v>46064.97597511574</v>
@@ -4565,10 +4572,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4584,13 +4591,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q55" s="8">
         <v>46122</v>
@@ -4610,7 +4617,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46064.97597422454</v>
@@ -4622,16 +4629,16 @@
         <v>46139.78107806713</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -4647,13 +4654,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q56" s="5">
         <v>46070</v>
@@ -4673,7 +4680,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B57" s="8">
         <v>46065.50497587963</v>
@@ -4685,16 +4692,16 @@
         <v>46139.78105626158</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -4710,13 +4717,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q57" s="8">
         <v>46104</v>
@@ -4736,7 +4743,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B58" s="5">
         <v>46064.97597565972</v>
@@ -4748,7 +4755,7 @@
         <v>46139.78125670139</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4772,7 +4779,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4785,7 +4792,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B59" s="8">
         <v>46064.975975925925</v>
@@ -4794,18 +4801,20 @@
         <v>46107.71502270833</v>
       </c>
       <c r="D59" s="8">
-        <v>46120.17345672454</v>
+        <v>46223.83490153935</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="I59" s="8">
         <v>46113</v>
       </c>
@@ -4822,13 +4831,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q59" s="8">
         <v>46119</v>
@@ -4848,7 +4857,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B60" s="5">
         <v>46064.97597623843</v>
@@ -4857,18 +4866,20 @@
         <v>46107.7136993287</v>
       </c>
       <c r="D60" s="5">
-        <v>46139.781139259256</v>
+        <v>46223.835005625</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
         <v>46120</v>
@@ -4883,13 +4894,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q60" s="5">
         <v>46118</v>
@@ -4909,7 +4920,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B61" s="8">
         <v>46064.9759734375</v>
@@ -4918,18 +4929,20 @@
         <v>46107.713914548614</v>
       </c>
       <c r="D61" s="8">
-        <v>46139.78116083333</v>
+        <v>46223.8351021875</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H61" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
         <v>46121</v>
@@ -4944,13 +4957,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q61" s="8">
         <v>46119</v>
@@ -4970,7 +4983,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B62" s="5">
         <v>46064.97597377315</v>
@@ -4982,7 +4995,7 @@
         <v>46139.78118356482</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5005,13 +5018,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q62" s="5">
         <v>46122</v>
@@ -5031,7 +5044,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B63" s="8">
         <v>46064.97597429398</v>
@@ -5040,18 +5053,20 @@
         <v>46107.71416802083</v>
       </c>
       <c r="D63" s="8">
-        <v>46126.207354363425</v>
+        <v>46223.83527831019</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
         <v>46125</v>
@@ -5066,13 +5081,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q63" s="8">
         <v>46125</v>
@@ -5092,7 +5107,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B64" s="5">
         <v>46064.97597454861</v>
@@ -5101,18 +5116,20 @@
         <v>46107.71432141204</v>
       </c>
       <c r="D64" s="5">
-        <v>46139.78120690973</v>
+        <v>46223.8353704051</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
         <v>46127</v>
@@ -5127,13 +5144,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q64" s="5">
         <v>46127</v>
@@ -5153,7 +5170,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B65" s="8">
         <v>46064.97597479167</v>
@@ -5165,7 +5182,7 @@
         <v>46198.63385799769</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5189,7 +5206,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5202,7 +5219,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B66" s="5">
         <v>46064.9759750463</v>
@@ -5214,16 +5231,16 @@
         <v>46198.63395618055</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5239,13 +5256,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q66" s="5">
         <v>46135</v>
@@ -5260,12 +5277,12 @@
         <v>31</v>
       </c>
       <c r="U66" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B67" s="8">
         <v>46064.97597528935</v>
@@ -5274,18 +5291,20 @@
         <v>46197.71009467593</v>
       </c>
       <c r="D67" s="8">
-        <v>46198.63395686343</v>
+        <v>46223.83550936343</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
         <v>46136</v>
@@ -5300,13 +5319,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q67" s="8">
         <v>46136</v>
@@ -5321,12 +5340,12 @@
         <v>31</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B68" s="5">
         <v>46064.975975532405</v>
@@ -5338,16 +5357,16 @@
         <v>46198.633957453705</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5363,13 +5382,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q68" s="5">
         <v>46139</v>
@@ -5381,15 +5400,15 @@
         <v>1</v>
       </c>
       <c r="T68" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="U68" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B69" s="8">
         <v>46064.975975787034</v>
@@ -5401,16 +5420,16 @@
         <v>46198.63395809028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5426,13 +5445,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q69" s="8">
         <v>46140</v>
@@ -5444,15 +5463,15 @@
         <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B70" s="5">
         <v>46064.97597357639</v>
@@ -5464,7 +5483,7 @@
         <v>46223.628154502316</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5488,7 +5507,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5501,7 +5520,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B71" s="8">
         <v>46064.97597436343</v>
@@ -5513,16 +5532,16 @@
         <v>46213.830161307866</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I71" s="8">
         <v>46142</v>
@@ -5540,13 +5559,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q71" s="8">
         <v>46150</v>
@@ -5558,15 +5577,15 @@
         <v>0</v>
       </c>
       <c r="T71" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B72" s="5">
         <v>46064.975974050925</v>
@@ -5578,16 +5597,16 @@
         <v>46213.83017636574</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I72" s="5">
         <v>46142</v>
@@ -5605,13 +5624,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q72" s="5">
         <v>46150</v>
@@ -5623,15 +5642,15 @@
         <v>0</v>
       </c>
       <c r="T72" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B73" s="8">
         <v>46090.53176077546</v>
@@ -5643,7 +5662,7 @@
         <v>46198.63384679398</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5667,7 +5686,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5680,7 +5699,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B74" s="5">
         <v>46090.53365568287</v>
@@ -5692,7 +5711,7 @@
         <v>46198.633871805556</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5719,13 +5738,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q74" s="5">
         <v>46149</v>
@@ -5737,15 +5756,15 @@
         <v>1</v>
       </c>
       <c r="T74" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B75" s="8">
         <v>46090.53385733796</v>
@@ -5757,7 +5776,7 @@
         <v>46198.63389696759</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5784,13 +5803,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q75" s="8">
         <v>46161</v>
@@ -5802,10 +5821,10 @@
         <v>1</v>
       </c>
       <c r="T75" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="269">
   <si>
     <t>50001514 - CLIENTE POR DEFINIR</t>
   </si>
@@ -4992,7 +4992,7 @@
         <v>46107.71404958333</v>
       </c>
       <c r="D62" s="5">
-        <v>46139.78118356482</v>
+        <v>46224.574943750005</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>223</v>
@@ -5001,9 +5001,11 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="6"/>
+        <v>88</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
         <v>46122</v>

--- a/data/50001514 - CLIENTE POR DEFINIR A.xlsx
+++ b/data/50001514 - CLIENTE POR DEFINIR A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="270">
   <si>
     <t>50001514 - CLIENTE POR DEFINIR</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>NATALYA ESPINOZA</t>
   </si>
   <si>
     <t>nespinoza@zitron.com</t>
@@ -2572,7 +2575,7 @@
         <v>88</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I22" s="5">
         <v>46062</v>
@@ -2596,7 +2599,7 @@
         <v>65</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q22" s="5">
         <v>46063</v>
@@ -2616,7 +2619,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="8">
         <v>46064.975973125</v>
@@ -2628,7 +2631,7 @@
         <v>46223.834713020835</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -2637,7 +2640,7 @@
         <v>88</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I23" s="8">
         <v>46063</v>
@@ -2661,7 +2664,7 @@
         <v>68</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="8">
         <v>46064</v>
@@ -2681,7 +2684,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B24" s="5">
         <v>46064.97597337963</v>
@@ -2693,7 +2696,7 @@
         <v>46155.82944616898</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>25</v>
@@ -2717,7 +2720,7 @@
         <v>26</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>26</v>
@@ -2730,7 +2733,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B25" s="8">
         <v>46064.97597363426</v>
@@ -2742,16 +2745,16 @@
         <v>46139.781813090274</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I25" s="8">
         <v>46064</v>
@@ -2769,13 +2772,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="8">
         <v>46069</v>
@@ -2795,7 +2798,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="5">
         <v>46064.98709253472</v>
@@ -2807,16 +2810,16 @@
         <v>46111.79073866898</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I26" s="5">
         <v>46064</v>
@@ -2834,13 +2837,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
@@ -2850,7 +2853,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" s="8">
         <v>46064.98694590278</v>
@@ -2862,16 +2865,16 @@
         <v>46111.790777268514</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I27" s="8">
         <v>46066</v>
@@ -2889,13 +2892,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
@@ -2905,7 +2908,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="5">
         <v>46064.975974479166</v>
@@ -2917,16 +2920,16 @@
         <v>46155.82950846065</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I28" s="5">
         <v>46064</v>
@@ -2944,13 +2947,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q28" s="5">
         <v>46121</v>
@@ -2970,7 +2973,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B29" s="8">
         <v>46064.97597476852</v>
@@ -2982,16 +2985,16 @@
         <v>46112.651016296295</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I29" s="8">
         <v>46064</v>
@@ -3009,13 +3012,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3023,15 +3026,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46064.975975023146</v>
@@ -3043,16 +3046,16 @@
         <v>46154.558014236114</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I30" s="5">
         <v>46073</v>
@@ -3070,13 +3073,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3084,15 +3087,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" s="8">
         <v>46064.97597528935</v>
@@ -3104,16 +3107,16 @@
         <v>46111.79066731481</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I31" s="8">
         <v>46064</v>
@@ -3131,13 +3134,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q31" s="8">
         <v>46084</v>
@@ -3157,7 +3160,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46064.97597284723</v>
@@ -3169,16 +3172,16 @@
         <v>46111.790595659724</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I32" s="5">
         <v>46064</v>
@@ -3196,13 +3199,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3210,15 +3213,15 @@
         <v>0</v>
       </c>
       <c r="T32" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46064.97597324074</v>
@@ -3230,16 +3233,16 @@
         <v>46111.79063912037</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I33" s="8">
         <v>46065</v>
@@ -3257,13 +3260,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3271,15 +3274,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46064.975973506946</v>
@@ -3291,16 +3294,16 @@
         <v>46111.79055864584</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I34" s="5">
         <v>46064</v>
@@ -3318,13 +3321,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q34" s="5">
         <v>46101</v>
@@ -3344,7 +3347,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46064.97597377315</v>
@@ -3356,16 +3359,16 @@
         <v>46111.79048188658</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I35" s="8">
         <v>46064</v>
@@ -3383,13 +3386,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>81</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3397,15 +3400,15 @@
         <v>0</v>
       </c>
       <c r="T35" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46064.975974050925</v>
@@ -3417,16 +3420,16 @@
         <v>46111.79051883102</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I36" s="5">
         <v>46073</v>
@@ -3444,13 +3447,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3458,15 +3461,15 @@
         <v>0</v>
       </c>
       <c r="T36" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46064.97597431713</v>
@@ -3478,16 +3481,16 @@
         <v>46111.79053048611</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I37" s="8">
         <v>46073</v>
@@ -3505,13 +3508,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3519,15 +3522,15 @@
         <v>0</v>
       </c>
       <c r="T37" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46064.97597459491</v>
@@ -3539,16 +3542,16 @@
         <v>46139.78184163195</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I38" s="5">
         <v>46065</v>
@@ -3566,13 +3569,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q38" s="5">
         <v>46091</v>
@@ -3592,7 +3595,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46064.97597487269</v>
@@ -3604,16 +3607,16 @@
         <v>46111.79036971065</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I39" s="8">
         <v>46065</v>
@@ -3631,13 +3634,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -3645,15 +3648,15 @@
         <v>0</v>
       </c>
       <c r="T39" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46064.97597515046</v>
@@ -3665,16 +3668,16 @@
         <v>46111.79041780093</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I40" s="5">
         <v>46076</v>
@@ -3692,13 +3695,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3706,15 +3709,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U40" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46064.97597454861</v>
@@ -3726,7 +3729,7 @@
         <v>46139.781639733796</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>25</v>
@@ -3750,7 +3753,7 @@
         <v>26</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -3763,7 +3766,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46070.66955917824</v>
@@ -3775,16 +3778,16 @@
         <v>46114.51383626157</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I42" s="5">
         <v>46063</v>
@@ -3802,13 +3805,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="5">
         <v>46069</v>
@@ -3828,7 +3831,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46064.97597483796</v>
@@ -3840,16 +3843,16 @@
         <v>46114.513888587964</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I43" s="8">
         <v>46084</v>
@@ -3867,13 +3870,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="8">
         <v>46090</v>
@@ -3893,7 +3896,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46087.50355304398</v>
@@ -3905,16 +3908,16 @@
         <v>46114.51393545139</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I44" s="5">
         <v>46091</v>
@@ -3932,13 +3935,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="5">
         <v>46091</v>
@@ -3958,7 +3961,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46087.50359630787</v>
@@ -3970,16 +3973,16 @@
         <v>46127.181483541666</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="8">
@@ -3995,13 +3998,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="8">
         <v>46126</v>
@@ -4021,7 +4024,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46064.97597513889</v>
@@ -4033,7 +4036,7 @@
         <v>46139.7815396875</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4057,7 +4060,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4070,7 +4073,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B47" s="8">
         <v>46064.97597543981</v>
@@ -4082,16 +4085,16 @@
         <v>46139.78147785879</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46094</v>
@@ -4109,13 +4112,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="8">
         <v>46097</v>
@@ -4135,7 +4138,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46064.97597572916</v>
@@ -4147,16 +4150,16 @@
         <v>46139.78149715278</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I48" s="5">
         <v>46098</v>
@@ -4174,13 +4177,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="5">
         <v>46099</v>
@@ -4200,7 +4203,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="8">
         <v>46064.975976030095</v>
@@ -4212,7 +4215,7 @@
         <v>46139.781448344904</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>25</v>
@@ -4236,7 +4239,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4249,7 +4252,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46064.975976319445</v>
@@ -4261,16 +4264,16 @@
         <v>46139.78134862268</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I50" s="5">
         <v>46100</v>
@@ -4288,13 +4291,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q50" s="5">
         <v>46104</v>
@@ -4314,7 +4317,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="8">
         <v>46064.97597666667</v>
@@ -4326,16 +4329,16 @@
         <v>46139.7813684838</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I51" s="8">
         <v>46105</v>
@@ -4353,13 +4356,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q51" s="8">
         <v>46111</v>
@@ -4379,7 +4382,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46064.9759734838</v>
@@ -4391,16 +4394,16 @@
         <v>46139.781402106484</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4416,13 +4419,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q52" s="5">
         <v>46112</v>
@@ -4442,7 +4445,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B53" s="8">
         <v>46064.975973865745</v>
@@ -4454,7 +4457,7 @@
         <v>46155.82935478009</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4478,7 +4481,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4491,7 +4494,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B54" s="5">
         <v>46064.97597451389</v>
@@ -4503,16 +4506,16 @@
         <v>46139.7811046412</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I54" s="6"/>
       <c r="J54" s="5">
@@ -4528,13 +4531,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46085</v>
@@ -4554,7 +4557,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
         <v>46064.97597511574</v>
@@ -4572,10 +4575,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I55" s="9"/>
       <c r="J55" s="8">
@@ -4591,13 +4594,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q55" s="8">
         <v>46122</v>
@@ -4617,7 +4620,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46064.97597422454</v>
@@ -4629,16 +4632,16 @@
         <v>46139.78107806713</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="5">
@@ -4654,13 +4657,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q56" s="5">
         <v>46070</v>
@@ -4680,7 +4683,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B57" s="8">
         <v>46065.50497587963</v>
@@ -4692,16 +4695,16 @@
         <v>46139.78105626158</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="8">
@@ -4717,13 +4720,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q57" s="8">
         <v>46104</v>
@@ -4743,7 +4746,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B58" s="5">
         <v>46064.97597565972</v>
@@ -4755,7 +4758,7 @@
         <v>46139.78125670139</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>25</v>
@@ -4779,7 +4782,7 @@
         <v>26</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -4792,7 +4795,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B59" s="8">
         <v>46064.975975925925</v>
@@ -4804,7 +4807,7 @@
         <v>46223.83490153935</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -4813,7 +4816,7 @@
         <v>88</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I59" s="8">
         <v>46113</v>
@@ -4831,13 +4834,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q59" s="8">
         <v>46119</v>
@@ -4857,7 +4860,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B60" s="5">
         <v>46064.97597623843</v>
@@ -4869,7 +4872,7 @@
         <v>46223.835005625</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
@@ -4878,7 +4881,7 @@
         <v>88</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -4894,13 +4897,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q60" s="5">
         <v>46118</v>
@@ -4920,7 +4923,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B61" s="8">
         <v>46064.9759734375</v>
@@ -4932,7 +4935,7 @@
         <v>46223.8351021875</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
@@ -4941,7 +4944,7 @@
         <v>88</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -4957,13 +4960,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q61" s="8">
         <v>46119</v>
@@ -4983,7 +4986,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B62" s="5">
         <v>46064.97597377315</v>
@@ -4995,7 +4998,7 @@
         <v>46224.574943750005</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5004,7 +5007,7 @@
         <v>88</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5020,13 +5023,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q62" s="5">
         <v>46122</v>
@@ -5046,7 +5049,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B63" s="8">
         <v>46064.97597429398</v>
@@ -5058,7 +5061,7 @@
         <v>46223.83527831019</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5067,7 +5070,7 @@
         <v>88</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5083,13 +5086,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q63" s="8">
         <v>46125</v>
@@ -5109,7 +5112,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5">
         <v>46064.97597454861</v>
@@ -5121,7 +5124,7 @@
         <v>46223.8353704051</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5130,7 +5133,7 @@
         <v>88</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="5">
@@ -5146,13 +5149,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q64" s="5">
         <v>46127</v>
@@ -5172,7 +5175,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B65" s="8">
         <v>46064.97597479167</v>
@@ -5184,7 +5187,7 @@
         <v>46198.63385799769</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>25</v>
@@ -5208,7 +5211,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>26</v>
@@ -5221,7 +5224,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B66" s="5">
         <v>46064.9759750463</v>
@@ -5233,16 +5236,16 @@
         <v>46198.63395618055</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I66" s="6"/>
       <c r="J66" s="5">
@@ -5258,13 +5261,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q66" s="5">
         <v>46135</v>
@@ -5279,12 +5282,12 @@
         <v>31</v>
       </c>
       <c r="U66" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B67" s="8">
         <v>46064.97597528935</v>
@@ -5296,7 +5299,7 @@
         <v>46223.83550936343</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5305,7 +5308,7 @@
         <v>88</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I67" s="9"/>
       <c r="J67" s="8">
@@ -5321,13 +5324,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q67" s="8">
         <v>46136</v>
@@ -5342,12 +5345,12 @@
         <v>31</v>
       </c>
       <c r="U67" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B68" s="5">
         <v>46064.975975532405</v>
@@ -5359,16 +5362,16 @@
         <v>46198.633957453705</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I68" s="6"/>
       <c r="J68" s="5">
@@ -5384,13 +5387,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q68" s="5">
         <v>46139</v>
@@ -5402,15 +5405,15 @@
         <v>1</v>
       </c>
       <c r="T68" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="U68" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B69" s="8">
         <v>46064.975975787034</v>
@@ -5422,16 +5425,16 @@
         <v>46198.63395809028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I69" s="9"/>
       <c r="J69" s="8">
@@ -5447,13 +5450,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q69" s="8">
         <v>46140</v>
@@ -5465,15 +5468,15 @@
         <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B70" s="5">
         <v>46064.97597357639</v>
@@ -5485,7 +5488,7 @@
         <v>46223.628154502316</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>25</v>
@@ -5509,7 +5512,7 @@
         <v>26</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>26</v>
@@ -5522,7 +5525,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B71" s="8">
         <v>46064.97597436343</v>
@@ -5534,16 +5537,16 @@
         <v>46213.830161307866</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I71" s="8">
         <v>46142</v>
@@ -5561,13 +5564,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q71" s="8">
         <v>46150</v>
@@ -5579,15 +5582,15 @@
         <v>0</v>
       </c>
       <c r="T71" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B72" s="5">
         <v>46064.975974050925</v>
@@ -5599,16 +5602,16 @@
         <v>46213.83017636574</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I72" s="5">
         <v>46142</v>
@@ -5626,13 +5629,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q72" s="5">
         <v>46150</v>
@@ -5644,15 +5647,15 @@
         <v>0</v>
       </c>
       <c r="T72" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B73" s="8">
         <v>46090.53176077546</v>
@@ -5664,7 +5667,7 @@
         <v>46198.63384679398</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -5688,7 +5691,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -5701,7 +5704,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B74" s="5">
         <v>46090.53365568287</v>
@@ -5713,7 +5716,7 @@
         <v>46198.633871805556</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5740,13 +5743,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q74" s="5">
         <v>46149</v>
@@ -5758,15 +5761,15 @@
         <v>1</v>
       </c>
       <c r="T74" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U74" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B75" s="8">
         <v>46090.53385733796</v>
@@ -5778,7 +5781,7 @@
         <v>46198.63389696759</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -5805,13 +5808,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q75" s="8">
         <v>46161</v>
@@ -5823,10 +5826,10 @@
         <v>1</v>
       </c>
       <c r="T75" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U75" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
